--- a/cockpit-data/story-log-last30days.xlsx
+++ b/cockpit-data/story-log-last30days.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -487,121 +487,121 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Life &amp; Annuities</t>
+          <t>Property &amp; Casualty</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Retirement</t>
+          <t>Health Insurance / Payer</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty</t>
+          <t>Brokers &amp; MGA/GA</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Investments</t>
+          <t>Wealth Management</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Wealth Management</t>
+          <t>Insurtech</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Brokers &amp; MGA/GA</t>
+          <t>Healthcare / Provider &amp; Clinical</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Life &amp; Annuities</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Insurtech</t>
+          <t>Retirement</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Health Insurance / Payer</t>
+          <t>Investments</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Healthcare / Provider &amp; Clinical</t>
+          <t>BrokerTech</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>BrokerTech</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -630,47 +630,47 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Technology &amp; AI</t>
+          <t>M&amp;A</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Investments &amp; Funding</t>
+          <t>Technology &amp; AI</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>M&amp;A</t>
+          <t>Regulatory &amp; Policy</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Regulatory &amp; Policy</t>
+          <t>Investments &amp; Funding</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27">
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30">
@@ -705,11 +705,21 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>2026-W27</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
           <t>2026-W28</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n">
-        <v>46</v>
+      <c r="B33" s="2" t="n">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -723,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -787,7 +797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -807,81 +817,81 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>BrokerTech Ventures names 2026 accelerator cohort of nine insurtech startups</t>
+          <t>Submissions-tool startup Sytrex rebrands as Braven after $4.6M seed and London launch</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>BrokerTech Ventures selected nine insurtech startups for its 2026 accelerator cohort, each receiving $50,000 in seed funding and access to BTV's broker and carrier distribution network to pilot their technology.</t>
+          <t>Formerly known as Sytrex, the insurance infrastructure startup raised a $4.6 million seed round led by Collide Capital, rebranded as Braven, and opened a London office to chase delegated-authority and specialty business.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>The Insurer</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/brokertech-ventures-announces-2026-accelerator-cohort-sponsors-global-insurance-symposium-and-announces-dates-for-brokertech-connect-2026-302729482.html</t>
+          <t>https://www.theinsurer.com/ti/news/insurtech-sytrex-raises-46-million-and-rebrands-to-braven-2026-06-16/</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>BrokerTech</t>
+          <t>Brokers &amp; MGA/GA</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>People &amp; Leadership</t>
+          <t>M&amp;A</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>UK/Europe</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>BrokerTech Ventures sets September dates for second annual BrokerTech Connect conference</t>
+          <t>ANV strikes deal for pan-European travel-protection MGA Assured Underwriting Group</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>BrokerTech Ventures announced its second annual BrokerTech Connect conference will convene C-suite executives from brokerages, carriers, wholesalers, and insurtech startups in Chicago on September 1-2, 2026.</t>
+          <t>Delegated-underwriting platform ANV agreed to buy London-based Assured Underwriting Group, the UK's top underwriter of travel-insurance bonds, from private-equity owner Mobeus, pending FCA approval expected to close in Q3 2026.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>Insurance Journal</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>http://www.prnewswire.com/news-releases/brokertech-ventures-announces-brokertech-connect-chicago-2026-bringing-together-insurance-and-insurtech-leaders-302804627.html</t>
+          <t>https://www.insurancejournal.com/news/international/2026/06/29/875674.htm</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -896,49 +906,49 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Acrisure completes acquisition of technology-driven property MGA Vave from Canopius</t>
+          <t>ANV rounds out workers' comp platform with wholesale agency purchase</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Acrisure finalized its purchase of Vave, Canopius Group's technology-driven property managing general agent, expanding Acrisure's specialty MGA distribution footprint.</t>
+          <t>ANV completed its acquisition of Associated Specialty Insurance Agency, a Pennsylvania wholesale agency with a 600-plus broker network focused on artisan contractor workers' comp risk, deepening ANV's specialty comp distribution alongside two other recent buys.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Reinsurance News</t>
+          <t>Insurance Journal</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://www.reinsurancene.ws/acrisure-completes-acquisition-of-mga-vave-from-canopius/</t>
+          <t>https://www.insurancejournal.com/news/east/2026/06/09/873014.htm</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Brokers &amp; MGA/GA</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>M&amp;A</t>
+          <t>Investments &amp; Funding</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -948,279 +958,279 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown completes acquisition of specialty MGU Accession Risk Management</t>
+          <t>Goldman Sachs leads $110M round for AI decisioning startup Taktile eyeing insurance claims</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Broker Brown &amp; Brown closed its acquisition of Accession Risk Management, a specialty managing general underwriter, broadening its wholesale distribution and underwriting capabilities.</t>
+          <t>Taktile raised a $110 million Series C led by Goldman Sachs Alternatives with Tiger Global and Index Ventures participating, positioning its AI decisioning platform to speed up high-stakes banking and insurance-claims calls.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Insurance Business America</t>
+          <t>Fortune</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://www.insurancebusinessmag.com/us/news/mergers-acquisitions/brown-and-brown-completes-acquisition-of-specialty-mgu-accession-risk-management-544903.aspx</t>
+          <t>https://fortune.com/2026/06/24/exclusive-taktile-goldman-sachs-ai-bank-insurance-funding/</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Brokers &amp; MGA/GA</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Market Economics</t>
+          <t>Technology &amp; AI</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>UK/Europe</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>MGA and MGU deal multiples hold firm as sector tops $102 billion in U.S. premium</t>
+          <t>HSBC signs multi-year AI alliance with Google Cloud</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Lower mid-market MGA and MGU businesses are transacting at 10-14x adjusted EBITDA while platform-scale groups clear 15-22x, as industry estimates put MGAs at more than $102 billion in annual U.S. premium volume.</t>
+          <t>HSBC entered a multi-year partnership with Google Cloud to embed AI more deeply across its banking and financial-services operations as part of a broader industry push toward cloud-based AI infrastructure.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>CT Acquisitions</t>
+          <t>FinTech Global</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://ctacquisitions.com/guides/specialty-insurance-mga-2026/</t>
+          <t>https://fintech.global/2026/06/17/hsbc-and-google-cloud-forge-multi-year-ai-partnership/</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Brokers &amp; MGA/GA</t>
+          <t>Health Insurance / Payer</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>People &amp; Leadership</t>
+          <t>Investments &amp; Funding</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>UK/Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Specialty group CFC names new group CEO</t>
+          <t>Medicare navigation platform Connie Health lands $40M and folds in Clearlink's Medicare book</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Specialty insurance group CFC named a new group chief executive expected to join during summer 2026 pending regulatory approval, with a 23-year company veteran serving as acting CEO in the interim.</t>
+          <t>Connie Health closed a $40 million Series B led by HealthQuest Capital while simultaneously completing its tenth acquisition, absorbing Clearlink Insurance Agency's Medicare business to scale its AI-driven senior-enrollment platform.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Insurance Business UK</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://www.insurancebusinessmag.com/us/news/breaking-news/cfc-names-new-group-ceo-581527.aspx</t>
+          <t>https://www.prnewswire.com/news-releases/connie-health-announces-acquisition-of-clearlink-insurance-agency-and-series-b-funding-to-accelerate-growth-in-medicare-302803979.html</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-18</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Health Insurance / Payer</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Technology &amp; AI</t>
+          <t>Market Economics</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Palantir expands AI partnership with Mexico's largest insurer GNP Seguros</t>
+          <t>Centene offers buyouts to most of its 61,000-person workforce as margins tighten</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Palantir Technologies expanded its enterprise agreement with GNP Seguros, its first publicly announced commercial customer in Latin America, to scale Foundry and AI Platform use across health, life, motor and property lines for fraud detection and claims.</t>
+          <t>Centene confirmed it is offering a voluntary separation program across the bulk of its employee base as the Medicaid-focused insurer works to cut costs amid declining earnings.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>FinTech Global</t>
+          <t>Becker's Payer Issues</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://fintech.global/2026/07/07/gnp-seguros-expands-ai-partnership-with-palantir/</t>
+          <t>https://www.beckerspayer.com/workforce/7-payers-cutting-jobs-2026/</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Health Insurance / Payer</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Technology &amp; AI</t>
+          <t>Regulatory &amp; Policy</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>UK/Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>ANNA Money embeds Admiral Business insurance directly into its small-business app</t>
+          <t>CMS floats rule locking in Medicare drug-price negotiation and new PBM reporting mandates</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Business account and tax platform ANNA Money partnered with Admiral Business to let small-business customers browse cover options, get information and obtain insurance quotes without leaving the ANNA app.</t>
+          <t>CMS proposed converting the IRA's Medicare Drug Price Negotiation Program into binding federal regulation starting plan year 2029 and opened comment on a framework requiring PBMs to report detailed drug pricing and rebate data.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>FinTech Global</t>
+          <t>Crowell &amp; Moring</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>https://fintech.global/2026/07/02/anna-money-brings-admiral-business-insurance-in-app/</t>
+          <t>https://www.crowell.com/en/insights/client-alerts/federal-roundup-updates-for-pbms-and-medicare-advantage-organizations</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Health Insurance / Payer</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>M&amp;A</t>
+          <t>Regulatory &amp; Policy</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>UK/Europe</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>SquareTrade launches licensed insurer entity in Brussels to reshape European strategy</t>
+          <t>IRDAI orders health insurers and hospitals onto new claims-speed and billing scorecards</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Warranty and protection-plan provider SquareTrade launched a newly licensed insurance entity in Brussels, bringing underwriting capabilities in-house as it accelerates growth across Europe.</t>
+          <t>India's insurance regulator introduced performance scorecards tracking claim settlement speed and billing accuracy for insurers and hospitals, alongside simpler standardized health policies meant to boost low insurance penetration.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>FinTech Global</t>
+          <t>Whalesbook</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://fintech.global/2026/07/06/squaretrade-reshapes-european-strategy-with-licensed-insurer/</t>
+          <t>https://www.whalesbook.com/news/English/insurance/Indias-IRDAI-Mandates-Health-Insurance-Overhaul-Simple-Policies-New-Scores/69cb73363f30946a7236b263</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Healthcare / Provider &amp; Clinical</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Investments &amp; Funding</t>
+          <t>M&amp;A</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1230,44 +1240,44 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>US fintech investment grows in Q2 2026 on 23% jump in larger deals</t>
+          <t>Ascension closes $3.9B AmSurg surgery-center deal after FTC-ordered divestitures</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>US fintech investment increased in the second quarter of 2026, driven by a 23% quarter-over-quarter rise in larger funding rounds, signaling renewed investor appetite for scaled fintech platforms.</t>
+          <t>Ascension completed its acquisition of ambulatory surgery operator AmSurg after agreeing to divest seven surgery centers to resolve FTC antitrust concerns, growing its ASC network to 300 centers across 35 states.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>FinTech Global</t>
+          <t>BenefitsPRO</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>https://fintech.global/2026/07/06/us-fintech-investments-grew-in-q2-2026-driven-by-a-23-qoq-rise-in-larger-deals/</t>
+          <t>https://www.benefitspro.com/amp/2026/06/04/ftc-clears-39b-ascension-amsurg-deal/</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Health Insurance / Payer</t>
+          <t>Healthcare / Provider &amp; Clinical</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Market Economics</t>
+          <t>M&amp;A</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1277,44 +1287,44 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Medicare Advantage penetration holds at 55% as UnitedHealth and Humana near half of enrollment</t>
+          <t>HCA Healthcare snaps up 17 urgent care clinics to expand Southeast footprint</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>KFF finds Medicare Advantage penetration steady at 55% as of July 1, 2026, with UnitedHealth Group and Humana together accounting for 46% of enrollees even as UnitedHealth's share slipped and Humana's grew.</t>
+          <t>HCA Healthcare acquired 17 urgent care clinics from Urgent Care Group across Charleston, Columbia, Myrtle Beach and Wilmington, rebranding them under its CareNow banner and pushing its urgent-care network past 390 locations.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>KFF</t>
+          <t>Spectrum News</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://www.kff.org/medicare/medicare-advantage-in-2026-enrollment-update-and-key-trends/</t>
+          <t>https://spectrumlocalnews.com/sc/south-carolina/news/2026/06/03/south-carolina-health-urgent-care</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Health Insurance / Payer</t>
+          <t>Healthcare / Provider &amp; Clinical</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Regulatory &amp; Policy</t>
+          <t>Technology &amp; AI</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1324,44 +1334,44 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>ACA insurers seek 10-20% premium increases for 2027 plans</t>
+          <t>WellSpan Health signs seven-year imaging and AI partnership with Philips</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Insurers filed proposed 2027 ACA marketplace premiums by the July 15 deadline, with most payers requesting increases in the 10-20% range, setting up another round of affordability debate ahead of open enrollment.</t>
+          <t>WellSpan Health launched a seven-year alliance with Philips to advance diagnostic imaging, AI-enabled tools and broader clinical innovation across its health system.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Healthcare Dive</t>
+          <t>Modern Healthcare</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>https://www.healthcaredive.com/news/affordable-care-act-premium-increase-2027-kff-peterson-center-healthcare/824695/</t>
+          <t>https://www.modernhealthcare.com/medical-devices/mh-wellspan-health-philips-imaging-ai-partnership/</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Health Insurance / Payer</t>
+          <t>Insurtech</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Regulatory &amp; Policy</t>
+          <t>Investments &amp; Funding</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1371,138 +1381,138 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Express Scripts becomes first major PBM to settle with FTC over insulin pricing practices</t>
+          <t>Nassau Financial backs AI-governance startup Trussed AI through its Reimagine program</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Cigna's Express Scripts settled FTC allegations that it inflated insulin costs through secretive manufacturer deals, agreeing to eliminate spread pricing and delink compensation from drug list prices ahead of 2027 reforms.</t>
+          <t>Nassau Financial Group made an undisclosed investment in Trussed AI, a platform that helps regulated enterprises audit and govern their AI systems, via Nassau's insurtech-focused Reimagine venture program.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>HLTH</t>
+          <t>BusinessWire</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://hlth.com/insights/articles/the-ftc-just-settled-with-a-pbm-what-s-actually-changing-in-drug-pricing</t>
+          <t>https://www.businesswire.com/news/home/20260617688261/en/Nassau-Financial-Group-Invests-in-Trussed-AI-to-Support-Responsible-Enterprise-AI-Adoption</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Health Insurance / Payer</t>
+          <t>Insurtech</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Regulatory &amp; Policy</t>
+          <t>Investments &amp; Funding</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>APAC</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Congress enacts PBM reforms delinking Medicare Part D compensation from drug prices</t>
+          <t>IAG's venture arm backs crisis-support app Sonder to extend care beyond claims</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>New federal legislation delinks pharmacy benefit manager compensation from drug prices in Medicare Part D, shifting to flat 'bona fide service fees' and prohibiting Medicaid spread pricing under a pass-through model.</t>
+          <t>Australia's IAG made a strategic minority investment in Sonder through its Firemark Ventures arm, aiming to extend the 24/7 mental-health and safety platform to customers during catastrophic weather events, not just its own workforce.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>AJMC</t>
+          <t>IAG Newsroom</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://www.ajmc.com/view/pbm-reforms-signed-into-law-reshaping-medicare-part-d-drug-pricing-transparency</t>
+          <t>https://www.iag.com.au/newsroom/company/iag-invests-in-sonder1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Healthcare / Provider &amp; Clinical</t>
+          <t>Investments</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Technology &amp; AI</t>
+          <t>Regulatory &amp; Policy</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>APAC</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>AI in APAC healthcare enters a new phase in 2026</t>
+          <t>IRDAI proposes letting insurers park up to 5% of surplus capital in private companies</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Asia-Pacific health systems are moving beyond pilot-stage AI deployments in 2026, with broader adoption of clinical decision support and imaging tools across the region's hospitals, per Healthcare IT News.</t>
+          <t>India's regulator floated rules allowing insurers to invest a portion of shareholder funds beyond the solvency margin into private limited companies, plus new repo and securities-lending powers for life insurers to manage liquidity.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Healthcare IT News</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://www.healthcareitnews.com/news/asia/apac-ai-healthcare-enters-new-phase-2026</t>
+          <t>https://www.business-standard.com/finance/insurance/irdai-proposes-investment-relaxation-for-insurers-in-private-companies-126061901310_1.html</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Healthcare / Provider &amp; Clinical</t>
+          <t>Investments</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Technology &amp; AI</t>
+          <t>Market Economics</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1512,185 +1522,185 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27% of health systems now hold commercial AI licenses to ease clinical workload</t>
+          <t>BlackRock winds down ESG-labeled target-date fund, thinning the sustainable-TDF field</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>A new survey finds 27% of U.S. health systems have signed commercial AI licenses aimed at reducing clinician workload, part of a broader push to integrate predictive AI tools with electronic health records.</t>
+          <t>BlackRock said it will liquidate its LifePath ESG Index Retirement Fund in October, leaving only Fidelity and GuideStone as managers still offering a dedicated sustainable target-date fund.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>PYMNTS</t>
+          <t>Sustainable Investing</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>https://www.pymnts.com/artificial-intelligence-2/2026/27percent-health-systems-have-commercial-ai-licenses</t>
+          <t>https://sustainableinvest.com/chart-of-the-week-july-6-2026-disappearing-dedicated-sustainable-tdfs/</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Healthcare / Provider &amp; Clinical</t>
+          <t>Life &amp; Annuities</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Technology &amp; AI</t>
+          <t>Regulatory &amp; Policy</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Health IT vendors roll out new radiology and nursing documentation AI tools</t>
+          <t>IRDAI chief says Bima Sugam marketplace will offer its first policies by September</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>A July 2026 health IT product roundup highlights new AI radiology draft-reporting tools designed to integrate with existing systems without platform migrations, alongside expanded ambient documentation tools for inpatient nursing workflows.</t>
+          <t>IRDAI chairman Ajay Seth said the long-awaited Bima Sugam digital insurance marketplace will launch initial motor, health and term products by end-September, with a separate consultation on distribution reforms due by end-July.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Healthcare NOW Radio</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>https://www.healthcarenowradio.com/health-it-product-news-report-july-2026/</t>
+          <t>https://www.business-standard.com/finance/insurance/bima-sugam-to-launch-initial-products-by-sept-end-irdai-chairman-seth-126063000744_1.html</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Insurtech</t>
+          <t>Life &amp; Annuities</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Investments &amp; Funding</t>
+          <t>People &amp; Leadership</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>APAC</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>AI-labeled startups capture record 95.2% of insurtech funding, Gallagher Re finds</t>
+          <t>Allianz Retire+ hires senior distribution lead as its guaranteed-income annuity gains adviser traction</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Global insurtech investment reached $1.63 billion in Q1 2026, up roughly 27% year-over-year, with AI-labeled companies accounting for a record 95.2% share of total funding according to Gallagher Re.</t>
+          <t>Allianz Retire+ reported a 31% jump in uptake of its AGILE lifetime-income product since January and named a new senior manager for retirement solutions to build on the momentum following recent fee cuts and product enhancements.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Insurance Business Magazine</t>
+          <t>AdviserVoice</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>https://www.insurancebusinessmag.com/reinsurance/news/breaking-news/ai-startups-capture-record-95-2-of-insurtech-funding--gallagher-re-574376.aspx</t>
+          <t>https://www.adviservoice.com.au/2026/06/allianz-retire-continues-momentum-with-strong-agile-growth-and-senior-distribution-appointment/</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Insurtech</t>
+          <t>Property &amp; Casualty</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Investments &amp; Funding</t>
+          <t>M&amp;A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>UK/Europe</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Poetic raises $50 million Series A for underwriting and compliance automation</t>
+          <t>Allianz eyes Portuguese insurer Caravela in deal that could nearly triple its local market share</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Insurtech Poetic secured a $50 million Series A round for its underwriting and compliance automation platform, with investors including Kleiner Perkins, Founders Fund, First Harmonic and OpenAI.</t>
+          <t>Allianz is reportedly in advanced talks to buy Caravela Seguros, Portugal's seventh-largest non-life insurer, a move that would lift Allianz's non-life market share in the country from roughly 1.3% to nearly 7% and push it past €1.15 billion in combined premiums.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Digital Insurance</t>
+          <t>Insurance Business</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>https://www.dig-in.com/news/top-insurtech-funding-rounds-june-2026</t>
+          <t>https://www.insurancebusinessmag.com/uk/news/mergers-acquisitions/allianz-in-advanced-talks-to-acquire-portuguese-insurer-caravela-seguros-report-577997.aspx</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Insurtech</t>
+          <t>Property &amp; Casualty</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Investments &amp; Funding</t>
+          <t>People &amp; Leadership</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1700,22 +1710,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Honeycomb Insurance raises $40 million for digital P&amp;C carrier build-out</t>
+          <t>AIG formally hands CEO reins to Eric Andersen as Zaffino moves to board chair</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Digital P&amp;C insurer Honeycomb Insurance raised $40 million from Zeev Ventures, Ibex Investors, Peakline and other investors to expand its underwriting technology and product lines.</t>
+          <t>AIG completed its planned leadership succession, with Eric Andersen becoming chief executive and joining the board while outgoing CEO Peter Zaffino shifts into the role of executive chairman.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Digital Insurance</t>
+          <t>Insurance Business</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>https://www.dig-in.com/news/top-insurtech-funding-rounds-june-2026</t>
+          <t>https://www.insurancebusinessmag.com/us/news/breaking-news/aig-completes-planned-ceo-transition-573286.aspx</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1727,106 +1737,106 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Insurtech</t>
+          <t>Property &amp; Casualty</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Technology &amp; AI</t>
+          <t>Market Economics</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>AI collapses insurance quote turnaround from days to minutes, industry data shows</t>
+          <t>US P&amp;C insurers post strong 92.4 combined ratio as premium growth cools sharply</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Industry data cited alongside recent insurtech funding rounds shows AI enabling submission-to-quote timelines to shrink from three days to three minutes and straight-through processing rates to jump from 10-15% to 70-90%.</t>
+          <t>Verisk and APCIA reported that US property-casualty carriers notched a 92.4 combined ratio and roughly $15.8 billion in underwriting gains for Q1 2026, even as premium growth decelerated markedly from prior years.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Digital Insurance</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>https://www.dig-in.com/news/top-insurtech-funding-rounds-june-2026</t>
+          <t>https://www.verisk.com/company/newsroom/u.s.-pc-insurers-post-strong-92.4-combined-ratio-as-premium-growth-slows-sharply/</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-23</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Investments</t>
+          <t>Retirement</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Investments &amp; Funding</t>
+          <t>Technology &amp; AI</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Insurance asset managers hunt for private-market opportunities as credit spreads stay tight</t>
+          <t>Ascensus and Voya team up on pooled retirement plan for mid-size and large employers</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>With traditional credit spreads historically compressed, insurance asset managers are increasingly diversifying into private markets and alternative assets to sustain investment income, per a Pensions &amp; Investments special report.</t>
+          <t>FuturePlan by Ascensus launched the PATH Pooled Employer Plan with Voya serving as recordkeeper and trustee and Mesirow providing fiduciary investment oversight, aiming to bring institutional-grade governance to a broader swath of employers.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Pensions &amp; Investments</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>https://www.pionline.com/institutional-investors/pi-insurance-asset-management-special-report-main-story-2026/</t>
+          <t>https://www.prnewswire.com/news-releases/futureplan-launches-path-pep-in-collaboration-with-voya-financial-bringing-institutional-retirement-capabilities-to-the-mid--and-large-market-302803768.html</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-18</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Investments</t>
+          <t>Retirement</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1836,143 +1846,143 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>UK/Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>AXA balances insurance growth against long-term investment ambitions</t>
+          <t>Recordkeepers warn fee compression is becoming an existential threat at industry roundtable</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>AXA is weighing continued insurance business expansion against its longer-horizon investment strategy as it navigates a shifting rate and asset-allocation environment.</t>
+          <t>At the 8th Annual RPA Record Keeper Roundtable, industry leaders described a squeeze between shrinking fees and rising demands for AI, cybersecurity and expanded participant services, while eyeing financial wellness as a growth avenue.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>AD-HOC-NEWS</t>
+          <t>401(k) TV</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/axa-balances-insurance-growth-and-long-term-investment-ambitions/69682677</t>
+          <t>https://401ktv.com/future-prospects-challenges-insights-from-the-rpa-record-keeper-roundtable/</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Investments</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Investments &amp; Funding</t>
+          <t>Technology &amp; AI</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Mercer flags top investment considerations for insurers navigating 2026</t>
+          <t>AI-native insurer Corgi launches full-service claims TPA with 5,000 adjusters</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Mercer's 2026 market outlook highlights the investment themes insurers should weigh this year, including rate normalization, private-asset allocation, and portfolio resilience.</t>
+          <t>Corgi Insurance rolled out Corgi Claims, a third-party administrator that pairs a nationwide adjuster network with AI that scores severity and flags coverage gaps the instant a claim is filed, serving carriers, MGAs and self-insured programs across major commercial lines.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Mercer</t>
+          <t>The Insurer</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>https://www.mercer.com/insights/investments/market-outlook-and-trends/top-investment-considerations-for-insurers/</t>
+          <t>https://www.theinsurer.com/ti/news/corgi-launches-ai-enabled-tpa-2026-06-29/</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Investments</t>
+          <t>Wealth Management</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Investments &amp; Funding</t>
+          <t>M&amp;A</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Mitigata secures $15 million to expand India cyber insurance underwriting</t>
+          <t>Modern Wealth notches 22nd deal with $1.1B Florida RIA acquisition</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>India-focused insurtech Mitigata raised $15 million to build out cyber insurance coverage and risk-assessment tools for Indian businesses, part of a broader wave of AI-labeled underwriting funding.</t>
+          <t>Modern Wealth Management agreed to acquire Clearwater-based Flaharty Asset Management, adding roughly $1.1 billion in client assets and an 18-person team as it pushes total AUM past $14 billion.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Digital Insurance</t>
+          <t>BusinessWire</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>https://www.dig-in.com/news/top-insurtech-funding-rounds-june-2026</t>
+          <t>https://www.businesswire.com/news/home/20260603035654/en/Modern-Wealth-Management-Expands-Florida-Footprint-with-Acquisition-of-$1.1B-Flaharty-Asset-Management</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Life &amp; Annuities</t>
+          <t>Wealth Management</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Market Economics</t>
+          <t>M&amp;A</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1982,44 +1992,44 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>LIMRA projects 2026 U.S. annuity sales to hold above $450 billion after fourth straight record year</t>
+          <t>Waverly Advisors makes first trust-company purchase, buying $3B Smithfield Trust</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>LIMRA's latest outlook shows retail annuity sales finishing 2025 above $460 billion, with 2026 sales expected to stay above $450 billion as fixed and fixed-indexed products keep gaining share over traditional variable annuities.</t>
+          <t>Birmingham-based Waverly Advisors acquired Pittsburgh's Smithfield Trust Company in its first dedicated trust acquisition, pushing the RIA's total assets under management well past $35 billion.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>LIMRA</t>
+          <t>citybiz</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>https://www.limra.com/en/newsroom/industry-trends/2026/the-2026-annuity-sales-outlook-remains-strong/</t>
+          <t>https://www.citybiz.co/article/861687/waverly-advisors-expands-trust-services-with-acquisition-of-smithfield-trust-company/</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Life &amp; Annuities</t>
+          <t>Wealth Management</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Market Economics</t>
+          <t>M&amp;A</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2029,39 +2039,39 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Life insurers enter 2026 with strong capital buffers and steady annuity demand</t>
+          <t>Modera Wealth adds $312M Florida RIA to expand state footprint</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>InvestmentNews reports life insurers begin 2026 on solid footing, citing robust capital strength and continued consumer demand for annuities as key stabilizers for the sector heading into the year.</t>
+          <t>Modera Wealth Management, a roughly $17.5 billion RIA, agreed to acquire Northstar Financial Planners, a Florida-based advisory firm managing about $311.6 million in client assets.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>InvestmentNews</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>https://www.investmentnews.com/life-insurance-and-annuities/life-insurers-entered-2026-on-firm-footing-as-capital-strength-and-annuity-demand-hold/265147</t>
+          <t>https://www.prnewswire.com/news-releases/modera-wealth-management-expands-florida-presence-with-northstar-transaction-302800947.html</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Life &amp; Annuities</t>
+          <t>Wealth Management</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2071,237 +2081,237 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>APAC</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>PayPay completes purchase of majority stake in T&amp;D Financial Life Insurance</t>
+          <t>Creative Planning deepens Southwest Florida push with accounting-firm acquisition</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Japanese fintech PayPay finalized its acquisition of a 70.2% stake in T&amp;D Financial Life Insurance Company from T&amp;D Holdings, marking a notable fintech entry into life insurance underwriting.</t>
+          <t>National RIA Creative Planning agreed to acquire MarkhamNorton Accountants+Advisors, a 45-year-old Southwest Florida tax and advisory firm, in a deal expected to close July 1.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>SEC EDGAR / PayPay Corp Form 6-K</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0002080845/000208084526000016/payp-ex99_1.htm</t>
+          <t>https://www.prnewswire.com/news-releases/creative-planning-expands-presence-in-southwest-florida-with-acquisition-of-markhamnorton-accountantsadvisors-302801745.html</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Life &amp; Annuities</t>
+          <t>Wealth Management</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Technology &amp; AI</t>
+          <t>M&amp;A</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>UK/Europe</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Life and annuity carriers move from AI pilots to permanent transformation in 2026</t>
+          <t>NatWest finalizes £2.7B Evelyn Partners buy, creating UK's biggest wealth manager</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Industry analysis frames 2026 as the year carriers shift from experimenting with AI in underwriting and fraud prevention toward embedding it permanently, even as regulators push for stronger data integrity and cybersecurity standards.</t>
+          <t>NatWest completed its acquisition of Evelyn Partners, combining Evelyn's £69 billion in assets under management with NatWest's £59 billion private banking book to form a roughly £127 billion combined wealth platform.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>InsuranceNewsNet</t>
+          <t>Willow Private Finance</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>https://insurancenewsnet.com/innarticle/the-forces-shaping-life-and-annuities-in-2026</t>
+          <t>https://www.willowprivatefinance.co.uk/natwest-completes-evelyn-partners-acquisition-as-wealth-and-property-advice-become-increasingly-connected</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Life &amp; Annuities</t>
+          <t>BrokerTech</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Regulatory &amp; Policy</t>
+          <t>Technology &amp; AI</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>IRDAI consults industry on insurer-funded policyholder protection fund</t>
+          <t>EZLynx Adds Real-Time Commercial Quoting Directly Into Agent Workflow</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>India's insurance regulator opened a consultation on whether insurers should make ongoing contributions to a new Policyholders' Education and Protection Fund, with industry comments due mid-July.</t>
+          <t>EZLynx launched Instant Commercial Quoting, surfacing real-time carrier quotes for general liability, BOP and workers' comp inside the submission workflow without a separate rater or portal, powered by the Ivans Distribution Platform.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Insurance Business Asia</t>
+          <t>EZLynx</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>https://www.insurancebusinessmag.com/asia/news/breaking-news/irdai-seeks-industry-input-on-insurerfunded-protection-scheme-580814.aspx</t>
+          <t>https://www.ezlynx.com/news/press-releases/2026/ezlynx-launches-instant-commercial-quoting-making-real-time-carrier-quotes-a-seamless-part-of-the-submission-workflow/</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty</t>
+          <t>Brokers &amp; MGA/GA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Market Economics</t>
+          <t>M&amp;A</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>UK/Europe</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>P&amp;C market enters correction phase with significant property rate relief</t>
+          <t>ANV Finalizes Purchase of London Wholesale Broker Iris Insurance Brokers</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>The U.S. property and casualty market is softening, with a quieter-than-expected 2025 hurricane season and record reinsurance capital driving rate decreases of 10-30% on shared and layered placements versus expiring terms.</t>
+          <t>ANV Group completed its acquisition of Iris Insurance Brokers, combining a Lloyd's wholesale brokerage, an intermediary platform and an MGA incubator to expand its UK and European specialty distribution reach.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Risk &amp; Insurance</t>
+          <t>Insurance Journal</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://riskandinsurance.com/pc-market-enters-correction-phase-with-significant-rate-relief-and-emerging-challenges/</t>
+          <t>https://www.insurancejournal.com/news/international/2026/07/07/876463.htm</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty</t>
+          <t>Brokers &amp; MGA/GA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Market Economics</t>
+          <t>People &amp; Leadership</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>APAC</t>
+          <t>UK/Europe</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Fitch keeps APAC insurance outlook neutral for 2026 despite rising claims costs</t>
+          <t>Bspoke Group's Tim Smyth Named New Chairman of the MGAA</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Fitch Ratings maintained a neutral 2026 outlook for Asia-Pacific insurers, citing capital buffers and disciplined underwriting offsetting rising claims costs, with non-life premium growth forecast at 2.5%.</t>
+          <t>The Managing General Agents' Association appointed Tim Smyth to succeed Charles Manchester as chairman following ten years in the role, effective around the trade body's annual conference.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>InsuranceAsiaNews</t>
+          <t>Insurance-Edge</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://insuranceasianews.com/apac-insurance-outlook-neutral-for-2026-despite-rising-claims-cost-fitch/</t>
+          <t>https://insurance-edge.net/2026/07/02/mgaa-appoints-new-chairman/</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty</t>
+          <t>Brokers &amp; MGA/GA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>People &amp; Leadership</t>
+          <t>M&amp;A</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2311,22 +2321,22 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Kellen Booher named President &amp; CEO of CopperPoint Insurance</t>
+          <t>Amwins Buys Texas Non-Subscriber Workplace Injury MGA Jackson-Lloyd</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>CopperPoint Insurance named Kellen Booher as its new President and CEO, a leadership transition for the workers' compensation-focused P&amp;C carrier.</t>
+          <t>Amwins Specialty Casualty Solutions acquired Jackson-Lloyd, a pioneer in non-subscriber occupational accident programs for Texas employers, adding to its accident and health portfolio.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>Insurance Journal</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/kellen-booher-named-president--ceo-of-copperpoint-insurance-302731454.html</t>
+          <t>https://www.insurancejournal.com/news/southcentral/2026/07/01/876010.htm</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2338,59 +2348,59 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty</t>
+          <t>Brokers &amp; MGA/GA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>People &amp; Leadership</t>
+          <t>M&amp;A</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Progressive CFO to step down in July 2026 after a decade in the role</t>
+          <t>Gallagher Expands Western Canada Presence With Wilson M. Beck Acquisition</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Progressive's long-serving CFO is set to step down in July 2026, capping roughly 35 years with the auto and property insurer including a decade as chief financial officer.</t>
+          <t>Arthur J. Gallagher acquired Burnaby-based commercial broker Wilson M. Beck Insurance Services in a deal described as among the largest ever completed in the Canadian market, deepening its construction and surety practices.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Life Insurance International</t>
+          <t>Canadian Underwriter</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>https://www.lifeinsuranceinternational.com/news/progressive-cfo-step-down-july-2026/</t>
+          <t>https://canadianunderwriter.ca/2026/07/07/gallagher-notches-major-canadian-acquisition/</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty</t>
+          <t>Brokers &amp; MGA/GA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2405,12 +2415,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>India raises insurer penalties tenfold under new insurance law amendments</t>
+          <t>IRDAI Plans to Overhaul Agent Commission Structure to Curb Mis-Selling</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>The maximum penalty for violations of India's Insurance Act and IRDAI Act increased tenfold, from ₹1 crore to ₹10 crore, under the newly enacted Sabka Bima Sabki Raksha (Amendment of Insurance Laws) Act.</t>
+          <t>India's insurance regulator is preparing a consultation paper that would spread distributor commissions over a policy's full life instead of paying them upfront, aiming to reduce mis-selling driven by front-loaded incentives.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -2420,29 +2430,29 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/amp/finance/insurance/irdai-proposes-framework-for-regulation-making-public-consultations-126061701305_1.html</t>
+          <t>https://www.business-standard.com/finance/insurance/irdai-plans-overhaul-of-commission-rules-to-curb-insurance-misselling-126070300966_1.html</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Retirement</t>
+          <t>Health Insurance / Payer</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Technology &amp; AI</t>
+          <t>Regulatory &amp; Policy</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2452,22 +2462,22 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Human Interest to take over 401(k) recordkeeping for UBS</t>
+          <t>CMS Launches Medicare GLP-1 Bridge Offering $50 Weight-Loss Drug Copay</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Human Interest will provide 401(k) recordkeeping services for UBS, using automated workflows integrated with over 500 payroll providers to track ACH debits, contribution flows, and funding status.</t>
+          <t>CMS's new Medicare GLP-1 Bridge took effect July 1, 2026, giving eligible Part D beneficiaries with qualifying conditions access to drugs like Zepbound and Wegovy for a flat $50 monthly copay through the end of 2027.</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>401(k) Specialist</t>
+          <t>CMS</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>https://401kspecialistmag.com/human-interest-to-provide-recordkeeping-for-ubs/</t>
+          <t>https://www.cms.gov/newsroom/press-releases/coming-soon-cms-provide-50-monthly-access-glp-1-medications-medicare-beneficiaries</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -2479,12 +2489,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Retirement</t>
+          <t>Health Insurance / Payer</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2499,22 +2509,22 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Early look at 'How America Saves' 2026 points to record 401(k) balances on auto-enrollment strength</t>
+          <t>More Health Systems Cut Ties With Medicare Advantage Plans Over Denials</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>A preview of Vanguard's forthcoming How America Saves 2026 report suggests automatic enrollment and auto-escalation features are pushing account balances to new highs despite market volatility.</t>
+          <t>A growing number of hospitals and health systems are dropping certain Medicare Advantage contracts in 2026, citing persistent prior-authorization denials and slow reimbursement from payers.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>401(k) Specialist</t>
+          <t>Becker's Hospital Review</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>https://401kspecialistmag.com/how-america-saves-2026-preview-strong-market-auto-features-power-record-401k-balances/</t>
+          <t>https://www.beckershospitalreview.com/finance/16-health-systems-dropping-medicare-advantage-plans-2026/</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2526,111 +2536,111 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Retirement</t>
+          <t>Healthcare / Provider &amp; Clinical</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Regulatory &amp; Policy</t>
+          <t>Technology &amp; AI</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2026 contribution limits rise to $24,500 for 401(k)-style plans</t>
+          <t>HOPPR Rolls Out AI Draft-Reporting Agent for Radiology Workflows</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>The 2026 contribution limit for workers under 50 in job-based retirement accounts rose to $24,500, while workers aged 50-59 and 64-plus gained an $8,000 catch-up allowance, up from $7,500 in 2025.</t>
+          <t>HOPPR commercially launched Presto, an AI reporting agent that drafts radiology reports directly inside existing systems like PowerScribe without requiring new software or platform migrations.</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>AARP</t>
+          <t>AuntMinnie</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>https://www.aarp.org/money/retirement/biggest-changes-2026/</t>
+          <t>https://www.auntminnie.com/imaging-informatics/artificial-intelligence/news/15828475/hoppr-launches-presto-ai-reporting-agent-for-radiology</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Retirement</t>
+          <t>Healthcare / Provider &amp; Clinical</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Market Economics</t>
+          <t>Technology &amp; AI</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>UK/Europe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>UK pension risk transfer market on pace for record £70 billion in 2026</t>
+          <t>Ambience Healthcare Expands AI Nursing Suite With Ambient Flowsheet Documentation</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Forecasts show the amount of UK defined-benefit pension risk transferred to insurers climbing roughly 15% in 2026 to about £70 billion, with the bulk annuity segment alone expected to top £50 billion for the first time.</t>
+          <t>Ambience Healthcare introduced Nursing Summary and Ambient Flowsheet Documentation tools that convert a nurse's spoken patient assessment directly into structured EHR entries, extending its inpatient AI system from pre-shift prep through charting.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Employee Benefits</t>
+          <t>HIT Consultant</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://employeebenefits.co.uk/pensions/pension-risk-transfer-market-forecast-to-reach-70-billion-in-2026/281865.article</t>
+          <t>https://hitconsultant.net/2026/06/23/ambience-healthcare-launches-inpatient-nursing-suite/</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-23</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Retirement</t>
+          <t>Healthcare / Provider &amp; Clinical</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Market Economics</t>
+          <t>M&amp;A</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2640,22 +2650,22 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>US pension risk transfer sales slipped to $49 billion in 2025 even as buy-in deals grew</t>
+          <t>Butler Memorial Hospital Moves Closer to Joining WVU Medicine Network</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>US pension risk transfer sales fell 6% year-over-year to $49 billion in 2025, but insurers report the buy-in segment kept expanding and expect that trend to continue through 2026.</t>
+          <t>Independence Health System's Butler Memorial Hospital is on track to join WVU Medicine this fall under a merger agreement that includes an $800 million capital investment, with $165 million earmarked specifically for Butler's facilities.</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Pensions &amp; Investments</t>
+          <t>Butler Eagle</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://www.pionline.com/institutional-investors/pension-risk-transfer/pi-pension-risk-transfer-2026-outlook-lawsuits/</t>
+          <t>https://www.butlereagle.com/20260701/the-road-to-merger-how-butlers-hospital-may-join-wvu-medicine/</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -2667,17 +2677,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>Insurtech</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Technology &amp; AI</t>
+          <t>Investments &amp; Funding</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2687,44 +2697,44 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Corgi Insurance launches AI-native third-party administrator Corgi Claims</t>
+          <t>Goldman-Led $110 Million Round Backs AI-Native Claims Automation Startup</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Corgi Insurance launched Corgi Claims, a full-service TPA pairing a nationwide network of more than 5,000 licensed adjusters with AI that reviews every claim on report, scoring severity and flagging coverage issues and missing documents.</t>
+          <t>A major funding round led by Goldman Sachs backed an AI claims automation platform that one large insurer is reportedly piloting to save more than $90 million, underscoring AI's dominance of insurtech investment dollars.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>FinanceX Magazine</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/corgi-insurance-launches-corgi-claims-the-ai-native-tpa-302813039.html</t>
+          <t>https://www.financexmagazine.com/post/insurtech-s-1-63b-tell-ai-is-no-longer-the-pitch-it-s-the-plumbing</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>Insurtech</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Market Economics</t>
+          <t>Technology &amp; AI</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2734,44 +2744,44 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Global insurance TPA market revenue grows by $32 billion year-over-year</t>
+          <t>Startup Corgi Launches AI-Native Platform to Speed Up Insurance Claims</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>A new market report finds the insurance third-party administrator sector's global revenue expanded by roughly $32 billion year-over-year, with AI-driven claims automation cited as a key growth driver through 2030.</t>
+          <t>Insurtech Corgi unveiled a new AI-driven platform designed to accelerate claims handling end-to-end for insurers.</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>GlobeNewswire</t>
+          <t>FinTech Global</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2026/04/27/3281499/0/en/insurance-third-party-administrators-tpas-global-market-report-2026-yoy-revenue-grew-by-32-billion-ai-driven-claims-automation-to-boost-insurance-tpa-growth-through-2030.html</t>
+          <t>https://fintech.global/2026/06/30/corgi-launches-ai-native-platform-accelerating-insurance-claims/</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Wealth Management</t>
+          <t>Investments</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>M&amp;A</t>
+          <t>Market Economics</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2781,44 +2791,44 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>RIA M&amp;A hits record $1.67 trillion in deal value in Q1 2026</t>
+          <t>Annuity-Embedded Target-Date Funds Near $42 Billion as Adoption Speeds Up</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Echelon Partners reports RIA merger-and-acquisition activity reached a new quarterly record in Q1 2026, with $1.67 trillion in cumulative deal value as consolidation among registered investment advisors accelerates.</t>
+          <t>Target-date fund series that embed guaranteed-income annuities grew nearly 70% year-over-year to about $42 billion across 13 series by the end of March 2026, with BlackRock's LifePath Paycheck line driving much of the gain.</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>InvestmentNews</t>
+          <t>401(k) Specialist</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://www.investmentnews.com/ria-news/ria-ma-hits-new-quarterly-record-in-q1-2026-with-167-trillion-in-deals/266421</t>
+          <t>https://401kspecialistmag.com/annuity-integrated-tdfs-reach-momentum/</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Wealth Management</t>
+          <t>Life &amp; Annuities</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>M&amp;A</t>
+          <t>Investments &amp; Funding</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2828,69 +2838,69 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Choreo continues acquisition run, adding Illinois-based RIA</t>
+          <t>Private Equity Firm Flexpoint Ford Takes Stake in Insurance Carrier Platform Novel Financial</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Choreo acquired an Illinois registered investment advisor as part of a string of 2026 deals under new CEO Jason Van de Loo, adding roughly $2 billion in combined assets under management this year.</t>
+          <t>Flexpoint Ford invested in Novel Financial Holdings, an independent holding company backing managing general underwriters and carriers that write roughly $2 billion in annual premium, broadening Novel's ownership base as it scales.</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>WealthManagement.com</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>https://www.wealthmanagement.com/ria-news/choreo-acquires-illinois-ria-with-700m-in-assets</t>
+          <t>https://www.prnewswire.com/news-releases/novel-financial-holdings-secures-investment-from-flexpoint-ford-302806069.html</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Wealth Management</t>
+          <t>Life &amp; Annuities</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Technology &amp; AI</t>
+          <t>Regulatory &amp; Policy</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Wealthtech roundup: AI-native platforms and prospecting tools gain traction among large RIAs</t>
+          <t>Foreign Investors Rush Into India's Insurance Sector After FDI Cap Removal</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>A weekly wealthtech roundup covers AI-native wealth manager Arca raising $64 million with backing from Vanguard's former CEO, and a $17 billion RIA naming a money-in-motion prospecting platform as its enterprise-wide tool.</t>
+          <t>With India's insurance FDI limit raised to 100%, IRDAI has already cleared one foreign investor's bid to raise its stake in a domestic venture and is reviewing another, signaling accelerating foreign entry into the market.</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>WealthTech Strategy</t>
+          <t>Republic World</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>https://www.wealthtechstrategy.com/post/the-wealthtech-safari-week-of-july-3-2026</t>
+          <t>https://www.republicworld.com/amp/business/foreign-insurers-knock-on-india-s-door-what-does-it-mean-for-india-s-insurance-sector-2026-07-03-131103</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2902,45 +2912,7142 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Property Catastrophe Reinsurance Prices Drop Sharply at Mid-Year Renewals</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Brokers reported risk-adjusted price cuts of roughly 15-40% across U.S. property treaty and facultative placements at the July 1 renewal date, as abundant capital and strong reinsurer profits softened the market.</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Insurance Journal</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.insurancejournal.com/news/international/2026/07/02/876137.htm</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Global Reinsurance Capital Hits Record $790 Billion, Tilting Leverage to Buyers</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>A surge in traditional and alternative capital pushed global reinsurer capital to an all-time high heading into the mid-year renewals, strengthening cedents' negotiating position on price and terms.</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Risk &amp; Insurance</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>https://riskandinsurance.com/reinsurance-buyers-gain-pricing-power-as-global-capital-hits-record-790-billion/</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>California's Insurance Chief Wins Court Fight Over Market-Stabilization Bulletins</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>A Los Angeles judge rejected a Consumer Watchdog lawsuit challenging Commissioner Ricardo Lara's bulletins limiting how much FAIR Plan wildfire losses insurers can pass on to policyholders, upholding his stabilization approach.</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>California Department of Insurance</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.insurance.ca.gov/0400-news/0100-press-releases/2026/release022-2026.cfm</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Report Finds Insurers' Policy Wording Changes Are Quietly Reducing Claim Volumes</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>New industry research shows shifts in coverage language and provisions are suppressing the number of claims filed, an underappreciated factor reshaping loss-cost trends across personal and commercial lines.</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Insurance Journal</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.insurancejournal.com/news/national/2026/07/08/876680.htm</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Retirement</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>FIS Prepares Cloud Overhaul of Its Dominant 401(k) Recordkeeping Systems</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>FIS Global Retirement is rolling out a new AI-enabled, cloud-based recordkeeping platform this July that unifies its legacy Omni and Relius systems, which together serve 650 clients and 68 million participants.</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>WealthManagement.com</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wealthmanagement.com/rpa-news/fis-new-cloud-based-record-keeping-system-could-unlock-the-potential-of-401-k-plans</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Retirement</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Wisconsin Retirement System Resets Retiree Insurance Premium Deduction Timing</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Wisconsin's Department of Employee Trust Funds implemented a one-time reset of annuity-deducted health and life insurance premiums for WRS retirees in July 2026 ahead of full payment-schedule alignment in August.</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Wisconsin Dept. of Employee Trust Funds</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>https://etf.wi.gov/news/retiree-insurance-premium-payment-changes-july-2026</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>TPA</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Horizon Opens HealthEZ TPA Platform to New Jersey Self-Funded Employers</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Horizon Blue Cross Blue Shield of New Jersey began accepting proposals on July 1, 2026 for its HealthEZ third-party administration platform targeting mid-sized self-funded employers, with plans taking effect January 1, 2027.</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>NJBIZ</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>https://njbiz.com/horizon-healthez-tpa-self-funded-plans-nj/</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Wealth Management</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Enhancement Group Notches Third Billion-Dollar-Plus Acquisition of the Year</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>The national RIA absorbed 88-year-old New York advisory firm Shufro-Glass Group in a roughly $760 million deal, pushing its total client assets above $157 billion.</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>WealthManagement.com</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wealthmanagement.com/ria-news/wealth-enhancement-pens-3rd-1b-plus-deal-in-2026</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Management</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Trio of Focus Financial Network Firms Merge to Form $10 Billion RIA</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Coastal Bridge Advisors completed a three-way combination with Waddell &amp; Associates and One Charles Private Wealth, creating a single advisory firm with more than $10 billion in assets across seven offices.</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>InvestmentNews</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.investmentnews.com/ria-news/coastal-bridge-advisors-seals-three-way-tie-up-to-create-10-billion-ria/267258</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Management</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Technology &amp; AI</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Orion Becomes One of the First Wealthtech Platforms Certified Under Global AI Governance Standard</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Orion Advisor Solutions earned ISO/IEC 42001 certification for the AI management system behind its Denali intelligence layer, joining a small group of tech firms with the credential.</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Business Wire</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.businesswire.com/news/home/20260629832926/en/Orion-Among-the-First-in-Wealthtech-to-Earn-ISO-42001-the-International-AI-Management-System-Standard</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Management</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>UK/Europe</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>WealthAi and Flanks Partner to Clean Up Fragmented Advisor Data</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>The two wealthtech vendors are combining AI-driven workflow automation with aggregated, compliant portfolio data to help wealth managers streamline front-to-back-office operations and cut costs.</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>FinTech Global</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>https://fintech.global/2026/07/07/wealthai-and-flanks-unite-to-fix-wealth-data-woes/</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>BrokerTech</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Vertafore ships new AI agents to automate agency email and reconciliation work</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Vertafore released Velocity AI Email and Reconciliation Agents inside its AgencyOne platform, aiming to cut manual processing time in independent agencies by up to 80% while keeping staff in the approval loop.</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Vertafore</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vertafore.com/resources/media-coverage/vertafore-releases-two-velocity-ai-agents</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>FinTech</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Investments &amp; Funding</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Goldman Sachs leads $110M round for AI decisioning startup serving banks and insurers</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Taktile raised a Goldman Sachs-led Series C bringing its total funding to $184 million, building an agentic platform that turns AI models into automated decision-makers for underwriting, claims and fraud triage at financial institutions.</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>The AI Insider</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>https://theaiinsider.tech/2026/07/01/taktile-secures-110m-in-goldman-sachs-led-series-c-to-power-ai-transformation-in-financial-institutions/</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Health Insurance / Payer</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>CMS switches on Medicare GLP-1 Bridge with $50 flat copay for weight-loss drugs</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Starting July 1, 2026, CMS's new Medicare GLP-1 Bridge demonstration gives eligible Part D beneficiaries access to Wegovy, Zepbound and similar GLP-1 medications for a flat $50 monthly copay through the end of 2027, with Humana administering the program.</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>CMS</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cms.gov/newsroom/press-releases/cms-launches-medicare-glp-1-bridge-expanding-access-glp-1-medications</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Health Insurance / Payer</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>IRDAI clears the way for multi-year health policies as medical inflation bites</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>India's insurance regulator is letting insurers sell three-to-five-year health policies with continuity benefits like waiting-period carry-forward, as insurers such as ICICI Lombard urge customers toward higher sum-insured coverage.</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Bima Bazaar</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>https://bimabazaar.com/2026-insurance-times/health-insurance-for-july-2026</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Health Insurance / Payer</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>People &amp; Leadership</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Cigna hands CEO reins to Brian Evanko as Cordani steps back</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>The Cigna Group elevated President and COO Brian Evanko to succeed David Cordani as chief executive effective July 1, 2026, with Evanko also joining the company's board.</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Life Insurance International</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lifeinsuranceinternational.com/news/cigna-brian-evanko-next-ceo/</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Healthcare / Provider &amp; Clinical</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Northwell and Nuvance finalize merger, creating a $22.6 billion New York-Connecticut system</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Northwell Health completed its merger with Nuvance Health, forming a combined system of 28 hospitals and over 1,000 care sites with $22.6 billion in revenue and more than 100,000 employees.</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Chief Healthcare Executive</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chiefhealthcareexecutive.com/view/northwell-health-nuvance-health-complete-merger-forming-22-6b-hospital-system</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Healthcare / Provider &amp; Clinical</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>HOPPR debuts Presto agent to slot AI draft reporting into radiologists' existing tools</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>HOPPR commercially launched Presto, an AI agent that drafts radiology reports directly inside systems like PowerScribe without requiring a new platform, pulling structured findings into radiologists' own templates.</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/hoppr-launches-presto-unlocking-ai-draft-reporting-in-existing-radiology-workflows-302808773.html</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Healthcare / Provider &amp; Clinical</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Ambience Healthcare expands ambient AI into inpatient nursing documentation</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Ambience Healthcare rolled out a Nursing Suite adding automated shift summaries and ambient flowsheet documentation, aiming to cut manual charting burden for inpatient nurses while keeping clinicians reviewing every entry.</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Business Wire</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.businesswire.com/news/home/20260623636774/en/Ambience-Healthcare-Introduces-Nursing-Suite-to-Extend-System-of-Intelligence-Across-Inpatient-Nursing</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Insurtech</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Investments &amp; Funding</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru cyber insurtech Mitigata lands $15M Series B from Bessemer</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Mitigata, an IRDAI-regulated cyber insurance broker serving over 800 organizations, raised a $15 million Series B led by Bessemer Venture Partners to expand its combined security, compliance and insurance platform.</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>FinTech Global</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>https://fintech.global/2026/06/24/mitigata-raises-15m-series-b-for-ai-cyber-resilience/</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Insurtech</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>UK/Europe</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>France's KAPIA-RGI snaps up Cegid Assurex to widen personal insurance software suite</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>KAPIA-RGI acquired Cegid Assurex Solutions, adding capabilities across annuities, provident benefits, retirement savings and tax-withholding administration to its personal insurance software offering in France.</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Las Vegas Sun (wire)</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>https://lasvegassun.com/news/2026/jul/07/rgi-group-strengthens-its-personal-insurance-capab/</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>US ETF inflows smash records, topping $1 trillion at the year's halfway mark</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Second-quarter inflows into US-listed ETFs hit a record $560 billion, pushing first-half totals over $1 trillion and putting the industry on pace for roughly $2.3 trillion for the full year, per State Street's flow data.</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Advisor Perspectives (VettaFi)</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.advisorperspectives.com/commentaries/2026/07/02/inside-the-etf-industrys-record-breaking-first-half-of-the-year</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Life &amp; Annuities</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Fixed annuity rates hold near 15-year highs even as Fed easing looms</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Top multi-year guaranteed annuity rates are sitting around 6.3%, well above comparable CD yields, though brokers expect rates to soften gradually as the Federal Reserve continues cutting.</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Annuity.org</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.annuity.org/annuities/rates/</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Aon: record $790 billion in reinsurance capital reshapes mid-year renewal pricing</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Aon's midyear renewal report shows global reinsurance capital hit an all-time high of $790 billion as of March 31, 2026, driving property-catastrophe price cuts of up to 25% for top-performing accounts.</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Reinsurance News</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reinsurancene.ws/record-790bn-reinsurance-capital-underpins-softer-mid-year-renewals-aon/</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>APAC</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Singapore regulator floats protected-cell structure to grow alternative risk transfer</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>MAS opened a consultation on a protected cell company framework meant to let Singapore compete for captive insurance, insurance-linked securities and sovereign risk-pooling business, running through early August.</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Insurance Business Asia</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.insurancebusinessmag.com/asia/news/breaking-news/singapore-targets-captive-insurance-with-proposed-pcc-framework-581727.aspx</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Retirement</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Empower to absorb Milliman's retirement recordkeeping arm in $340 million deal</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Empower agreed to buy Milliman's retirement and benefits administration business, picking up roughly 1,100 defined-contribution plans and 400 defined-benefit plans covering more than $130 billion in combined assets, while Milliman keeps its actuarial consulting unit.</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Business Wire</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.businesswire.com/news/home/20260630508272/en/Empower-to-Acquire-Millimans-Retirement-Administration-Business</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Retirement</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Annuities creep into more target-date funds, but plan adoption stays cautious</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Assets in target-date strategies embedding annuities nearly doubled year over year to about $44 billion, yet that remains under 1% of the broader $4.8 trillion target-date market as plan sponsors continue weighing guaranteed-income options.</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/06/25/annuity-options-are-growing-in-401ks-but-adoption-remains-limited.html</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Management</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Savant Wealth Management plants its flag in Maine via Richard Brothers tie-up</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Savant closed a partnership with South Portland-based Richard Brothers Financial Advisors, adding about $240 million in client assets and giving the RIA its first Maine office among 70 locations nationwide.</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>InvestmentNews</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.investmentnews.com/ria-news/savant-wealth-management-enters-maine-with-latest-acquisition/267244</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Management</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Enhancement to absorb 88-year-old New York advisory practice in $760M deal</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Enhancement agreed to acquire the Shufro-Glass Group from Shufro Rose, a two-advisor Manhattan team managing over $760 million, pushing its aggregate client assets past $157 billion.</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>InvestmentNews</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.investmentnews.com/ria-news/wealth-enhancement-to-absorb-88-year-old-new-york-advisory-dynasty-in-760m-deal/267236</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>BrokerTech</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Vertafore rolls out AI agents to automate agency email and reconciliation work</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Vertafore released two new Velocity AI agents built into its AgencyOne platform, one handling inbound email triage and one automating reconciliation, with early testing showing up to 80% faster email processing for independent agencies.</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Insurance Edge</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>https://insurance-edge.net/2026/07/01/vertafore-releases-two-velocity-ai-agents/</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Brokers &amp; MGA/GA</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Investments &amp; Funding</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Catastrophe-property MGU pulls in $460 million-plus as admitted carriers retreat from Florida and Texas</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>A continuation vehicle led by Lexington Partners and Barings poured more than $460 million into a catastrophe-exposed property managing general underwriter, capital meant to let it keep writing coverage in states where standard insurers are pulling back.</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>InsurTech.ME</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.insurtech.me/blog/2026/7/5/insurance-insurtech-iinvestment-intelligence-report-week-of-june-28-july-4-202</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Brokers &amp; MGA/GA</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>UK/Europe</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Lloyd's MGA launches data-backed deductible buy-down cover for renewable energy sites</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Africa Speciality Risks, a Lloyd's MGA, launched what it calls the world's first data-enabled deductible buy-down product for renewable energy assets, giving brokers independently verified real-time asset data to negotiate better underwriting terms.</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Insurance Edge</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>https://insurance-edge.net/2026/07/01/samp-risk-launches-deductible-buy-down-product/</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Brokers &amp; MGA/GA</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>People &amp; Leadership</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>UK/Europe</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Acrisure's UK arm loses its CEO and CFO/COO in abrupt leadership shake-up</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Acrisure UK chief executive Mark Mcilquham and CFO/COO Katherine Cross both had their roles terminated, with interim leadership handed to Andrew Boyce and Eleanor Gamble as the broker platform's UK retail business regroups.</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Insurance Times</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.insurancetimes.co.uk/news/acrisure-uk-chief-executive-and-cfo/coo-resign/1459019.article</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>FinTech</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Matic scoops up Policygenius' home and auto book alongside new PE backing</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Embedded insurance platform Matic secured a minority growth investment from Primus Capital while simultaneously acquiring nearly 30,000 property and casualty policies from Policygenius, folding those customers into its 70-plus carrier marketplace.</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>GlobeNewswire</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2026/06/24/3317007/0/en/matic-secures-minority-investment-from-primus-capital-and-acquires-policygenius-property-and-casualty-insurance-book.html</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Health Insurance / Payer</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>New York's Essential Plan cliff hits roughly 450,000 immigrant enrollees this month</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>About 450,000 New Yorkers, largely lawfully present immigrants, lost Essential Plan coverage as of July 1 after federal budget law changes eliminated their ACA subsidy eligibility, pushing them onto marketplace plans with premiums and cost-sharing.</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Fiscal Policy Institute</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>https://fiscalpolicy.org/regional-impacts-of-the-july-2026-essential-plan-cliff</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Health Insurance / Payer</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Investments &amp; Funding</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Value-based Medicare tech firm Pearl Health raises $110 million to expand payer partnerships</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Pearl Health closed a $110 million raise, a $50 million equity round led by Andreessen Horowitz plus a $60 million credit facility, to grow its AI clinical intelligence platform used by providers and payers managing Medicare risk contracts.</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Axios</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/pro/health-tech-deals/2026/07/07/pearl-health-raise-medicare-tech</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Healthcare / Provider &amp; Clinical</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>US age-adjusted death rate hits a record low as CDC releases fresh 2025 data</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Provisional CDC data published July 2 showed the nation's age-adjusted death rate fell 4.6% in 2025 to 689.2 per 100,000 people, the lowest rate ever recorded, a data point providers and payers are citing in mortality and underwriting trend discussions.</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Alston &amp; Bird (Health Care Week in Review)</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.alston.com/en/insights/publications/2026/07/health-care-week-in-review-july-2-2026</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Insurtech</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Investments &amp; Funding</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru cyber-insurance startup Mitigata raises $15 million Series B led by Bessemer</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Mitigata, which combines cybersecurity monitoring with cyber insurance for Indian businesses, closed a $15 million Series B led by Bessemer Venture Partners to expand internationally and scale its AI-powered security operations center.</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.business-standard.com/companies/start-ups/cybersecurity-startup-mitigata-raises-15-mn-in-bessemer-led-series-b-round-126062301118_1.html</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Fidelity to bolt guaranteed lifetime income onto its target-date fund lineup</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Fidelity is launching Freedom Lifetime, a suite of target-date collective investment trusts that let plan sponsors offer employees the option to convert part of their target-date balance into a guaranteed income stream, available on Fidelity's recordkeeping platform in early 2027.</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Business Wire</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.businesswire.com/news/home/20260610197394/en/Fidelity-Investments-to-Expand-Target-Date-Lineup-With-Launch-of-Guaranteed-Income-Solution</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Life &amp; Annuities</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>UK/Europe</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>UK regulator's funded reinsurance crackdown could reshape bulk annuity deals</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>The Bank of England's Prudential Regulation Authority is pushing ahead with Consultation Paper CP8/26, which would roughly double or more the capital insurers must hold against funded reinsurance used heavily in pension risk transfer deals; the consultation window closes July 31, 2026.</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Insurance Business UK</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.insurancebusinessmag.com/reinsurance/news/breaking-news/pra-moves-to-tighten-capital-rules-on-funded-reinsurance-573597.aspx</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>New York rolls out fresh guidance aimed at bringing down auto insurance premiums</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Governor Hochul directed the state's Department of Financial Services to issue new guidance implementing FY2027 budget reforms intended to lower New York auto insurance rates and crack down on fraudulent claims, effective July 1.</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Office of Governor Kathy Hochul</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.governor.ny.gov/news/governor-hochul-issues-new-guidance-implement-reforms-aimed-lowering-auto-insurance-premiums</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Allegheny Health Network's insurance parent finances hospital tie-up with $285 million pledge</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>As Heritage Valley Health System formally joined Allegheny Health Network on July 1, insurer parent Highmark and the merging systems jointly committed roughly $285 million over a decade to fund clinical and IT upgrades, underscoring how payer-provider capital is intertwined in the deal.</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/heritage-valley-health-system-enters-new-era-as-part-of-allegheny-health-network-302815526.html</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>TPA</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>DOL's proposed PBM fee-disclosure rule set to reach TPAs for plan years starting July 2026</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>A Department of Labor proposal would force pharmacy benefit managers and the TPAs and insurers that administer PBM services for self-funded ERISA health plans to make detailed compensation disclosures, with applicability proposed for plan years beginning on or after July 1, 2026.</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>U.S. Department of Labor / Federal Register</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.federalregister.gov/documents/2026/01/30/2026-01907/improving-transparency-into-pharmacy-benefit-manager-fee-disclosure</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Management</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Hightower's acquisitive Signature Wealth unit lands three more advisory teams worth $5 billion</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Hightower's Signature Wealth division added Private Vista, Hightower Great Lakes and The McGuirk &amp; De Nevi Group in a combined deal bringing roughly $5 billion in assets, pushing its year-to-date total past $25 billion added through conversions and acquisitions.</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>InvestmentNews</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.investmentnews.com/ria-news/hightower-signature-wealth-adds-5-billion-in-deal-hat-trick/267291</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Management</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Enhancement adds an 88-year-old New York advisory shop in a $760 million deal</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>National RIA aggregator Wealth Enhancement agreed to acquire the Shufro-Glass Group from Shufro Rose, a firm founded in 1938, adding more than $760 million in client assets and pushing Wealth Enhancement's total assets above $157 billion.</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/wealth-enhancement-to-acquire-the-shufro-glass-group-of-shufro-rose-with-over-760-million-in-client-assets-302814088.html</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>BrokerTech</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>White Glove Insurance spins up brokerage tech subsidiary</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>White Glove Insurance launched White Glove Technology, a new subsidiary building a full-service platform meant to consolidate the fragmented vendor stack independent brokerages rely on, with a phased rollout planned through Q4 2026.</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>24-7PressRelease</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.24-7pressrelease.com/press-release/536466/white-glove-insurance-to-launch-subsidiary-white-glove-technology-that-focuses-on-a-full-service-technology-platform-for-insurance-brokerage-firms</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Brokers &amp; MGA/GA</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>People &amp; Leadership</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>UK/Europe</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>MGAA installs Bspoke Group's Tim Smyth as new chairman</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>The UK's Managing General Agents' Association named Tim Smyth, chair of Bspoke Group, as its new chairman, succeeding Charles Manchester after his decade-long tenure leading the trade body.</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>PropertyCasualty360</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.propertycasualty360.com/2026/07/06/people-on-the-move-in-the-pc-insurance-industry-july-3-2026/</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Brokers &amp; MGA/GA</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>People &amp; Leadership</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Alliant lures former Hub executive to lead expanded M&amp;A advisory push</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Alliant Insurance Services named Justin Sorensen, formerly a Hub International practice leader, to the newly created role of executive vice president within Alliant's mergers and acquisitions advisory team, reporting to the president of Alliant P&amp;C.</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Insurance Journal</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.insurancejournal.com/news/midwest/2026/07/02/876155.htm</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Health Insurance / Payer</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Medicare beneficiaries get $50-a-month GLP-1 weight-loss drug access under new CMS bridge program</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>CMS's new Medicare GLP-1 Bridge program, which took effect July 1, lets eligible Part D beneficiaries access Wegovy and Zepbound for weight management at a flat $50 monthly copay through the end of 2027, marking the first time Medicare has covered GLP-1s for weight loss.</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/06/30/medicare-obesity-drug-glp-1-coverage-starting-july-1.html</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Health Insurance / Payer</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Florida's top cancer center drops out of Humana Medicare Advantage network</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Moffitt Cancer Center became out-of-network for Humana Medicare Advantage PPO and HMO plans starting July 1, forcing Tampa-area cancer patients to weigh higher out-of-pocket costs or switch coverage, though Humana may extend continuity-of-care exceptions through year-end.</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>FOX 13 Tampa Bay</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fox13news.com/news/some-humana-medicare-advantage-plans-will-be-out-network-moffitt-cancer-center-starting-july</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Healthcare / Provider &amp; Clinical</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Judge forces Mississippi Medicaid to pay Delta hospital to avert closure</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>A Mississippi Chancery Court judge ordered the state's Medicaid division to release a $2.4 million payment to Greenwood Leflore Hospital, averting an imminent shutdown while a planned takeover by the University of Mississippi Medical Center proceeds.</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Becker's Hospital Review</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.beckershospitalreview.com/finance/mississippi-judge-orders-state-medicaid-officials-to-pay-hospital-2-4-million-keep-it-open-through-july/</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Healthcare / Provider &amp; Clinical</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI leans on Sam Altman to court hospitals for its healthcare push</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI is pitching hospitals directly, with CEO Sam Altman personally engaging health systems, as the company rolls out ChatGPT for Clinicians and a consumer 'ChatGPT Health' feature while competing with Anthropic and Google for enterprise healthcare business.</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Forbes</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.forbes.com/sites/amyfeldman/2026/07/07/how-openai-plans-to-win-over-doctors-patients-and-hospitals/</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Insurtech</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Investments &amp; Funding</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Goldman-led $110 million round backs AI claims automation platform Taktile</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Goldman Sachs led a $110 million investment into Taktile, with one major insurer reportedly modeling more than $90 million in claims savings from adopting the AI decisioning platform, in one of the quarter's largest insurtech rounds.</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>InsurTech.ME</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.insurtech.me/blog/2026/6/27/insurance-insurtech-investment-intelligence-report-week-of-june-2127-2026</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Insurtech</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Insurers' AI pilots keep stalling before they reach production</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>A growing share of insurer AI pilots fail to graduate into production deployments, with industry analysts pointing to weak data foundations and unclear ROI cases as the main reasons projects stall despite heavy AI investment across the sector.</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>FinTech Global</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>https://fintech.global/2026/07/01/why-ai-pilots-are-failing-insurers-and-what-comes-next/</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Insurtech</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>People &amp; Leadership</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>New Indian institute launches insurtech leadership training program at GIFT City</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>NeoProEd kicked off the first cohort of its Insurtech Professional Program in partnership with GIFT International FinTech Institute, a 10-week practitioner-led course capped by a residential capstone in Gandhinagar aimed at building India's next generation of insurance and insurtech leaders.</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>ANI News</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aninews.in/news/business/neoproed-launches-to-build-indias-next-generation-of-insurance-amp-insurtech-leaders20260703171028/</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Insurtech</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>APAC</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Asia's largest insurtech gathering spotlights agentic AI and underinsurance</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>ITC Asia 2026 drew more than 1,500 industry leaders to Singapore for sessions on turning agentic AI into measurable underwriting and claims ROI, alongside dedicated tracks on Japan's evolving insurance ecosystem and expanding coverage across India.</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>InsureTech Connect Asia</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>https://asia.insuretechconnect.com/insights</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Allianz and Zurich launch joint blended-finance vehicle with government backers</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Allianz and Zurich, alongside AXA and Canadian pension giant La Caisse, launched Scaled Development, a platform meant to mobilize private capital for sustainable projects in emerging markets, with Germany and Canada committing initial public capital of up to €130 million.</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>The Insurer</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theinsurer.com/sustainable-insurance/news/allianz-and-zurich-form-blended-finance-investment-company-for-sustainable-2026-07-06/</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Life &amp; Annuities</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>ICICI Prudential Life seeks reclassification of Prudential as investor amid Bharti Life buyout</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>As Prudential moves to take a 75% controlling stake in Bharti Life Insurance, ICICI Prudential Life's board asked regulators to reclassify Prudential Corporation Holdings from a promoter to an investor and is weighing a rename to ICICI Life, with both promoters signing a letter of undertaking on July 4 to manage the conflict of interest.</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.business-standard.com/companies/news/icici-pru-life-seeks-investor-status-for-prudential-after-bharti-life-deal-126070500585_1.html</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Swiss Re projects sharpest slowdown in global non-life premium growth in over a decade</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Swiss Re Institute forecasts real non-life premium growth will slow to just 0.6% in 2026, far below the 3.6% long-term trend, as competitive pricing and softer economic momentum weigh on advanced markets while insurer ROE eases from its 2025 peak.</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Reinsurance News</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reinsurancene.ws/swiss-re-institute-forecasts-non-life-premium-growth-to-slow-to-0-6-in-2026/</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>JPMorgan sees no floor yet for falling reinsurance prices after steep midyear drop</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>JPMorgan analysts say property catastrophe reinsurance rates fell roughly 16% at the July 1 renewal, an acceleration from January, as record capital and low catastrophe losses continue shifting pricing power toward cedents with little sign of stabilizing.</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Reinsurance News</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reinsurancene.ws/unlikely-a-floor-will-be-found-on-reinsurance-pricing-in-the-near-term-jp-morgan/</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>People &amp; Leadership</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>UK/Europe</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Willis Re adds veteran marine broker to reinsurance team</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Willis Re hired David Kim, a 20-year marine and non-marine reinsurance veteran and former Korean Re London chief executive, as a reinsurance broker to bolster its marine practice.</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Reinsurance News</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reinsurancene.ws/willis-re-hires-david-kim-as-reinsurance-broker/</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Management</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>UK/Europe</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>European wealth managers rethink how they welcome crypto-derived fortunes</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Private banks including Dutch wealth manager Van Lanschot Kempen are shifting from treating crypto wealth holders with suspicion to actively courting them, pairing compliance specialists with family-office style services to capture the 'new wealthy.'</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>FinTech Global</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>https://fintech.global/2026/07/01/welcoming-the-new-wealthy/</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Management</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Investments &amp; Funding</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>WealthTech leads another active week of fintech fundraising</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Wealthtech startups accounted for five of the 17 fintech funding deals tracked in the first days of July, continuing a strong run for advisor- and RIA-focused technology investment following a record Q1 for the category.</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>FinTech Global</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>https://fintech.global/2026/07/03/here-are-the-17-deals-recorded-by-fintechs-this-week-read-them-all-here/</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>BrokerTech</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>AI-linked layoffs ripple through tech and finance sectors, insurance included</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>A labor-market analysis found tech and finance employers, including insurance-adjacent firms, are shedding roughly 28,000 jobs a month as AI automation reshapes staffing needs across broker and carrier back offices.</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Insurance Journal</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.insurancejournal.com/news/national/2026/07/02/875989.htm</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Brokers &amp; MGA/GA</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>MGA premiums surge to $108.7 billion in 2025 as capacity providers grow choosier</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>AM Best's annual MGA segment report found delegated-authority premium jumped nearly 18% in 2025, marking a fifth straight year of double-digit growth, though analysts flagged tighter carrier scrutiny of capacity deployment ahead.</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>Risk &amp; Insurance</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>https://riskandinsurance.com/mga-premiums-hit-108-7-billion-in-2025-as-capacity-scrutiny-tightens/</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Health Insurance / Payer</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>ACA marketplace insurers propose another double-digit premium jump for 2027</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>A KFF analysis of 77 insurers' rate filings found a median proposed 2027 ACA premium increase of 14%, following 2026's 20% median hike, driven by rising costs, regulatory changes and the expiration of enhanced subsidies.</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Axios</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.axios.com/2026/07/08/obamacare-aca-premiums-price-jump</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Health Insurance / Payer</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Roughly 450,000 immigrants lose New York's Essential Plan coverage as eligibility rules tighten</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>New York's Essential Plan enrollees between 200-250% of the federal poverty level, including many lawfully present immigrants, lost coverage on July 1, 2026 after federal changes eliminated the subsidies that made the expanded program financially viable.</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>NY Focus</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>https://nysfocus.com/2026/06/26/new-york-essential-plan-coverage-confusion</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Healthcare / Provider &amp; Clinical</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>People &amp; Leadership</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>MemorialCare's longtime CEO Barry Arbuckle steps up to executive chairman</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>After more than two decades leading MemorialCare, Barry Arbuckle moved into a new executive chairman role effective July 1, 2026, with Dr. David Kim succeeding him as president and CEO in a long-planned succession.</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Becker's Hospital Review</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.beckershospitalreview.com/hospital-executive-moves/48-recent-hospital-health-system-executive-moves-2-2/</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Healthcare / Provider &amp; Clinical</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>UK/Europe</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>UK unveils new framework to cut heart disease and stroke deaths</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>The UK government launched a Cardiovascular Disease Modern Service Framework setting 12 near-term priorities aimed at preventing thousands of premature heart disease and stroke deaths annually through earlier diagnosis and more consistent care.</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>GOV.UK</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/news/new-heart-disease-and-strokes-plan-to-saves-thousands-of-lives</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Healthcare / Provider &amp; Clinical</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>AI tool wins first-of-its-kind FDA clearance for detecting hidden heart disease from routine ECGs</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Pathway Labs' EchoNext became the first FDA-cleared AI tool to flag six types of structural heart disease from a standard 12-lead ECG, trained on hundreds of thousands of paired ECG-echocardiogram records and now being distributed via OpenEvidence.</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>STAT News</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.statnews.com/2026/06/23/pathway-labs-echonext-ai-tool-heart-disease-detection/</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Insurtech</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>UK/Europe</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Allianz Partners to cut up to 1,800 jobs as it leans further into AI</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Allianz's travel-and-assistance unit confirmed plans to eliminate as many as 1,800 European roles as part of a broader push to adopt AI across claims and customer service operations.</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>Insurance Journal</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.insurancejournal.com/news/international/2026/07/08/876625.htm</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>Lemonade trims reinsurance cession again in latest July renewal</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Lemonade reduced its quota-share cession to roughly 18% of premium from about 20% in its July 1, 2026 reinsurance renewal, a smaller adjustment than last year's steep cut, while expanding its European catastrophe protection.</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>Insurance Business Magazine</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.insurancebusinessmag.com/reinsurance/news/breaking-news/lemonade-trims-reinsurance-cession-further-in-july-renewal-580906.aspx</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Retirement</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>High earners lean on HSAs over 401(k) catch-ups as new Roth mandate takes effect</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>With 2026's requirement that catch-up contributions from workers earning over $150,000 be made on a Roth basis, advisors report high earners are increasingly prioritizing HSA contributions first for their triple tax advantage.</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>24/7 Wall St</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/personal-finance/2026/07/05/the-hsa-move-high-earners-are-prioritizing-over-401k-catch-up-contributions-in-2026/</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>BrokerTech</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>Matic buys Policygenius's 30,000-policy home and auto book, adds Primus Capital as investor</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Embedded insurance platform Matic acquired Policygenius's property and casualty insurance portfolio of nearly 30,000 policies and secured a minority growth investment from Primus Capital to fund further expansion.</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>The Insurer</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theinsurer.com/ti/news/matic-acquires-policygenius-pc-portfolio-secures-primus-capital-backing-2026-06-24/</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Brokers &amp; MGA/GA</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>Acrisure folds six specialty MGAs into new Asero Insurance Services brand</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Acrisure launched Asero Insurance Services to unify several of its program administrators, which collectively underwrite over $1 billion in premium for hard-to-place commercial risks, under one shared platform.</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Business Wire</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.businesswire.com/news/home/20260630604248/en/Acrisure-Introduces-Asero-Insurance-Services-Combining-Specialty-MGAs-under-a-Unified-Brand</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Brokers &amp; MGA/GA</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>People &amp; Leadership</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>UK/Europe</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>CFC recruits former Direct Line chief Adam Winslow as group CEO</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Specialty MGA CFC named Adam Winslow, formerly group CEO of Direct Line Group, as its next chief executive, succeeding Louise O'Shea as the company looks to accelerate international growth and AI adoption.</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Insurance Journal</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.insurancejournal.com/news/international/2026/07/07/876432.htm</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>FinTech</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Investments &amp; Funding</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru cyber insurance startup Mitigata lands $15 million Series B</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Mitigata, an IRDAI-regulated cyber insurance broker, raised a $15 million Series B led by Bessemer Venture Partners to expand its AI-powered cyber resilience platform internationally and scale its security operations center.</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>Inc42</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>https://inc42.com/buzz/cyber-risk-and-insurance-startup-mitigata-raises-15-mn/</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Health Insurance / Payer</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>People &amp; Leadership</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Brian Evanko takes the reins as Cigna's new CEO</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Brian Evanko officially became CEO of The Cigna Group on July 1, succeeding David Cordani, who moves into the role of executive chair after nearly 17 years leading the company.</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>Bloomberg</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/news/articles/2026-07-01/cigna-s-ceo-vows-to-put-patients-first-wall-street-is-watching</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Health Insurance / Payer</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>ACA marketplace enrollment drops by millions as subsidy fight continues</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>With enhanced ACA premium subsidies expired, marketplace enrollment has fallen by millions, and the Trump administration and policy analysts continue to disagree over how much of the drop reflects affordability versus fraud crackdowns.</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/07/03/aca-enrollment-enhanced-subsidies-lapse-fraud.html</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Health Insurance / Payer</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Elevance sues CMS seeking same Medicare Advantage star-rating fix given to Clover</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Elevance Health sued CMS and HHS, arguing it deserves the same star-ratings recalculation a court forced for Clover Health, a change Elevance says would be worth about $115 million in quality bonus payments.</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>STAT News</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.statnews.com/2026/07/02/elevance-lawsuit-medicare-advantage-star-ratings-clover/</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Insurtech</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>People &amp; Leadership</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>NeoProEd launches to close India's insurtech talent gap</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>NeoProEd, founded by veteran insurance leaders, launched its Insurtech Professional Program with the GIFT International FinTech Institute to train talent for India's fast-growing, AI- and embedded-insurance-driven sector.</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.business-standard.com/amp/content/press-releases-ani/neoproed-launches-to-build-india-s-next-generation-of-insurance-insurtech-leaders-126070400018_1.html</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Life &amp; Annuities</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>MassMutual climbs to No. 100 on Fortune 500 in its 175th anniversary year</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>MassMutual announced it rose to No. 100 on the 2026 Fortune 500 list, extending a streak of more than three decades on the ranking as the mutual insurer marks 175 years in business.</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Business Wire</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.businesswire.com/news/home/20260701497961/en/MassMutual-Ranks-No.-100-on-the-2026-Fortune-500-List</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>UK/Europe</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Softening P&amp;C market fuels fresh megadeal speculation, with Zurich-Beazley as bellwether</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Dealmakers point to Zurich's $10.9 billion all-cash agreement to acquire Lloyd's insurer Beazley as a sign more billion-dollar-plus insurance acquisitions could surface in the second half of 2026 as underwriting conditions soften.</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>The Insurer</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theinsurer.com/ti/news/ma-talk-builds-as-market-softens-2026-07-03/</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Property catastrophe reinsurance rates fall as much as 20% at mid-year Florida renewals</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Record capital from traditional and alternative sources pushed risk-adjusted property-catastrophe reinsurance pricing down roughly 15-20% at the June/July renewals, even as Florida cedents sought billions more in coverage.</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Insurance Business Magazine</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.insurancebusinessmag.com/reinsurance/news/breaking-news/record-capital-drives-softer-reinsurance-pricing-at-july-renewals-580902.aspx</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>APAC</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>Singapore regulator floats protected cell company framework for alternative risk transfer</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>The Monetary Authority of Singapore opened a consultation on a new Protected Cell Company legislative structure meant to deepen alternative risk transfer and collateralized reinsurance activity in the city-state.</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>Monetary Authority of Singapore</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mas.gov.sg/news/media-releases/2026/mas-consults-on-pcc-framework-to-support-growth-of-alternative-risk-transfer-solutions-in-insurance</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>TPA</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Virginia's tougher PBM and TPA oversight law takes effect</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>A new Virginia law effective July 1, 2026 expands regulation of PBMs and third-party administrators, banning practices like retroactive claim reductions and electronic claim-processing fees while mandating pass-through pricing.</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>Mintz</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mintz.com/insights-center/viewpoints/2146/2026-04-09-states-continue-advance-new-pbm-and-drug-pricing</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Management</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Enhancement scoops up second Shufro Rose team with $554 million in assets</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Enhancement agreed to acquire the Kaminsky-Silverman Group from New York-based Shufro Rose, its second deal with the firm in as many months, adding roughly $554 million in client assets.</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/wealth-enhancement-to-acquire-the-kaminsky-silverman-group-of-shufro-rose-with-over-554-million-in-client-assets-302816466.html</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>BrokerTech</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Independent agency Barge Group consolidates quoting on EZLynx's rating platform</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Barge Group adopted EZLynx's integrated personal-lines rater to enter risk data once and pull real-time quotes from multiple carriers, aiming to speed proposals and free up time for prospecting.</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>GlobeNewswire (via Manila Times)</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.manilatimes.net/2026/07/07/tmt-newswire/globenewswire/barge-group-selects-ezlynx-to-accelerate-quoting-and-win-more-business/2379986</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Brokers &amp; MGA/GA</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>UK/Europe</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Specialist Risk Group snaps up London MGA and wholesale broker Superian</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>SRG acquired Superian Insurance Group, a London wholesaler, retailer and MGA known for medical malpractice and healthcare liability expertise, expanding SRG's specialist distribution capacity.</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>Insurance Journal</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.insurancejournal.com/news/international/2026/07/02/876112.htm</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Brokers &amp; MGA/GA</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>People &amp; Leadership</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Liberty Mutual elevates Defne Turkes to lead its international insurance division</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Liberty Mutual named Defne Turkes president and managing director of Liberty International Insurance effective July 1, tasking her with growth across commercial and Asia retail markets.</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>Risk &amp; Insurance</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>https://riskandinsurance.com/defne-turkes-appointed-president-and-managing-director-of-liberty-international-insurance/</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Brokers &amp; MGA/GA</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>People &amp; Leadership</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>Aon installs Pedro Penalva as new CEO of Latin America</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Aon named Pedro Penalva CEO of Latin America effective July 1, reporting directly to CEO Greg Case, as part of a broader regional leadership reshuffle spanning EMEA and Latin America.</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Insurance Journal</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.insurancejournal.com/news/international/2026/05/19/870599.htm</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Brokers &amp; MGA/GA</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Investments &amp; Funding</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>MGA platform Novel Financial Holdings lands strategic backing from Flexpoint Ford</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Novel Financial Holdings, which oversees carriers writing about $2 billion in annual premium tied to managing general underwriters, received a growth investment from private equity firm Flexpoint Ford.</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>The Insurer</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theinsurer.com/program-manager/news/flexpoint-ford-invests-in-bredahl-led-novel-financial-holdings-2026-06-22/</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Health Insurance / Payer</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>Medicare's $50-a-month GLP-1 weight-loss drug bridge takes effect July 1</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Medicare Part D beneficiaries meeting BMI and health-condition criteria can now access GLP-1 obesity medications like Wegovy and Zepbound for $50 a month through 2027 under a new CMS pilot tied to manufacturer pricing deals.</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>AARP</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aarp.org/medicare/glp1-weight-loss-copay-program/</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Health Insurance / Payer</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>Payer stocks extend rally as UnitedHealth and Centene guidance eases cost-trend fears</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>UnitedHealth shares have climbed roughly 78% off their yearly low after Centene's stronger-than-expected medical loss ratio followed similar upbeat signals from UnitedHealth and Elevance, prompting analyst upgrades ahead of Q2 earnings.</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>Invezz</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>https://invezz.com/news/2026/06/30/up-by-80-does-the-unitedhealth-group-have-more-upside/</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Healthcare / Provider &amp; Clinical</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>UK/Europe</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>NHS delayed hospital discharges now cost £2.7 billion a year, King's Fund finds</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Analysis from the King's Fund shows the cost of patients stuck in hospital beds despite being medically fit for discharge rose 7.5% in a year, driven by strained social care and community services capacity.</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>Clinical Services Journal</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.clinicalservicesjournal.com/story/51973/delayed-discharges-cost-to-nhs-rises-7-5-to-2-7bn</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Healthcare / Provider &amp; Clinical</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>UK/Europe</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>NICE greenlights two non-invasive tests to cut years-long endometriosis diagnosis delays</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>NICE recommended NHS use of Endotest, a saliva-based biomarker test, and EndoSure, a gut-signal sensor test, for a three-year evidence-gathering period aimed at speeding endometriosis diagnosis in primary care.</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>NICE</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nice.org.uk/news/articles/new-technologies-for-endometriosis-diagnosis-in-primary-care</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Insurtech</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>Insurance Journal previews industry 'Demo Day' showcasing agentic AI underwriting tools</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>Insurance Journal spotlighted an upcoming Risky Future event where vendors will demo agentic AI tools built for underwriting, part of a broader industry push to move AI pilots into production for policy pricing.</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>Insurance Journal</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.insurancejournal.com/news/national/2026/07/07/876352.htm</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Insurtech</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>People &amp; Leadership</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>Claims-communication insurtech Kyber named a 2026 PropertyCasualty360 Insurance Luminary</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Kyber was recognized in PropertyCasualty360's 2026 Insurance Luminaries class for workplace culture, with founder and CEO Arvind Sontha honored as Rising Star of the Year.</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>EIN Presswire</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>https://tech.einnews.com/pr_news/924853969/kyber-selected-as-a-propertycasualty360-2026-insurance-luminaries-winner</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Insurtech</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>APAC</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>China issues first nationwide AI rulebook for banks and insurers</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>China's National Financial Regulatory Administration published guidelines spanning governance, data handling and risk management for AI use across the banking and insurance sectors, its first comprehensive framework of its kind.</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>The Asian Banker</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theasianbanker.com/updates-and-articles/pboc-s-ai-finance-strategy-signals-china-s-next-phase-of-fintech-reform</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Life &amp; Annuities</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>India's insurance regulator floats spreading agent commissions across a policy's full life</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>IRDAI is considering replacing large upfront commissions with payouts spread over the life of a policy to curb mis-selling, with a distribution consultation paper expected by end of July according to chairman Ajay Seth.</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>Insurance News BD</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>https://eng.insurancenewsbd.com/article/news/6707</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>US P&amp;C insurers swing to $16.3 billion underwriting gain in strongest Q1 in decades</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>The US property-casualty industry posted a $16.3 billion net underwriting gain in Q1 2026, reversing a year-earlier loss on lower catastrophe losses and easing incurred-loss trends, according to AM Best data.</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>Insurance Journal</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.insurancejournal.com/news/national/2026/06/23/874936.htm</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>UK/Europe</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>UK underwriting body warns dealmakers are leaning too hard on cyber cover</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>The International Underwriting Association cautioned that warranty-and-indemnity insurers may be over-relying on cyber insurance to cover M&amp;A transaction risk, flagging coverage gaps underwriters need to address.</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>Insurance-Edge</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>https://insurance-edge.net/2026/07/02/iua-warns-on-over-reliance-on-cyber-insurance/</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>UK/Europe</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>Pen Underwriting doubles UK SME cyber cover to £10 million as broker demand rises</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>MGA Pen Underwriting raised its cyber cover limit to £10 million for risks incepting from July 1 and brought claims handling in-house, responding to broker demand from larger SME clients.</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>The Insurer</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theinsurer.com/cyber-risk/news/pen-underwriting-doubles-uk-sme-cyber-cover-limit-2026-06-08/</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>TPA</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>People &amp; Leadership</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>Point32Health's TPA arm HPI names Tim O'Brien as president</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>Health Plans, Inc., a national third-party administrator of self-funded benefit plans, appointed Tim O'Brien president, bringing experience from leading Vitori Health through its sale to Global Excel Management.</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>PRWeb</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.prweb.com/releases/tim-obrien-to-lead-health-plans-inc-hpi-as-president-302805130.html</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Management</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>People &amp; Leadership</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>Steward Partners taps Sequoia Financial's Joseph Glick as new COO</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>Steward Partners, which now oversees more than $53 billion in assets, hired Joseph Glick away from Sequoia Financial Group to run operations, technology and finance as the firm scales.</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>http://www.prnewswire.com/news-releases/steward-partners-appoints-joseph-glick-as-chief-operating-officer-positioning-the-firm-for-its-next-phase-of-growth-302818560.html</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Management</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid RIA AmeriFlex reaches its $3 billion growth target six months ahead of schedule</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>The AmeriFlex Group added 18 advisors and more than $1.7 billion in client assets in the first half of 2026, crediting succession-matching tools for pulling forward its annual growth goal.</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/the-ameriflex-group-adds-more-than-1-7-billion-in-total-client-assets-in-first-half-2026--302817331.html</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>BrokerTech</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Investments &amp; Funding</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>BrokerTech Ventures names 2026 accelerator cohort of nine insurtech startups</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>BrokerTech Ventures selected nine insurtech startups for its 2026 accelerator cohort, each receiving $50,000 in seed funding and access to BTV's broker and carrier distribution network to pilot their technology.</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/brokertech-ventures-announces-2026-accelerator-cohort-sponsors-global-insurance-symposium-and-announces-dates-for-brokertech-connect-2026-302729482.html</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>BrokerTech</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>People &amp; Leadership</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>BrokerTech Ventures sets September dates for second annual BrokerTech Connect conference</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>BrokerTech Ventures announced its second annual BrokerTech Connect conference will convene C-suite executives from brokerages, carriers, wholesalers, and insurtech startups in Chicago on September 1-2, 2026.</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>http://www.prnewswire.com/news-releases/brokertech-ventures-announces-brokertech-connect-chicago-2026-bringing-together-insurance-and-insurtech-leaders-302804627.html</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>Brokers &amp; MGA/GA</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>Acrisure completes acquisition of technology-driven property MGA Vave from Canopius</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>Acrisure finalized its purchase of Vave, Canopius Group's technology-driven property managing general agent, expanding Acrisure's specialty MGA distribution footprint.</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>Reinsurance News</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reinsurancene.ws/acrisure-completes-acquisition-of-mga-vave-from-canopius/</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Brokers &amp; MGA/GA</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Brown &amp; Brown completes acquisition of specialty MGU Accession Risk Management</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>Broker Brown &amp; Brown closed its acquisition of Accession Risk Management, a specialty managing general underwriter, broadening its wholesale distribution and underwriting capabilities.</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>Insurance Business America</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.insurancebusinessmag.com/us/news/mergers-acquisitions/brown-and-brown-completes-acquisition-of-specialty-mgu-accession-risk-management-544903.aspx</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Brokers &amp; MGA/GA</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>MGA and MGU deal multiples hold firm as sector tops $102 billion in U.S. premium</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Lower mid-market MGA and MGU businesses are transacting at 10-14x adjusted EBITDA while platform-scale groups clear 15-22x, as industry estimates put MGAs at more than $102 billion in annual U.S. premium volume.</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>CT Acquisitions</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>https://ctacquisitions.com/guides/specialty-insurance-mga-2026/</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Brokers &amp; MGA/GA</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>People &amp; Leadership</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>UK/Europe</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>Specialty group CFC names new group CEO</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Specialty insurance group CFC named a new group chief executive expected to join during summer 2026 pending regulatory approval, with a 23-year company veteran serving as acting CEO in the interim.</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>Insurance Business UK</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.insurancebusinessmag.com/us/news/breaking-news/cfc-names-new-group-ceo-581527.aspx</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>FinTech</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>Palantir expands AI partnership with Mexico's largest insurer GNP Seguros</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>Palantir Technologies expanded its enterprise agreement with GNP Seguros, its first publicly announced commercial customer in Latin America, to scale Foundry and AI Platform use across health, life, motor and property lines for fraud detection and claims.</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>FinTech Global</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>https://fintech.global/2026/07/07/gnp-seguros-expands-ai-partnership-with-palantir/</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>FinTech</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>UK/Europe</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>ANNA Money embeds Admiral Business insurance directly into its small-business app</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>Business account and tax platform ANNA Money partnered with Admiral Business to let small-business customers browse cover options, get information and obtain insurance quotes without leaving the ANNA app.</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>FinTech Global</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>https://fintech.global/2026/07/02/anna-money-brings-admiral-business-insurance-in-app/</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>FinTech</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>UK/Europe</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>SquareTrade launches licensed insurer entity in Brussels to reshape European strategy</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>Warranty and protection-plan provider SquareTrade launched a newly licensed insurance entity in Brussels, bringing underwriting capabilities in-house as it accelerates growth across Europe.</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>FinTech Global</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>https://fintech.global/2026/07/06/squaretrade-reshapes-european-strategy-with-licensed-insurer/</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>FinTech</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Investments &amp; Funding</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>US fintech investment grows in Q2 2026 on 23% jump in larger deals</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>US fintech investment increased in the second quarter of 2026, driven by a 23% quarter-over-quarter rise in larger funding rounds, signaling renewed investor appetite for scaled fintech platforms.</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>FinTech Global</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>https://fintech.global/2026/07/06/us-fintech-investments-grew-in-q2-2026-driven-by-a-23-qoq-rise-in-larger-deals/</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Health Insurance / Payer</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>Medicare Advantage penetration holds at 55% as UnitedHealth and Humana near half of enrollment</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>KFF finds Medicare Advantage penetration steady at 55% as of July 1, 2026, with UnitedHealth Group and Humana together accounting for 46% of enrollees even as UnitedHealth's share slipped and Humana's grew.</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>KFF</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kff.org/medicare/medicare-advantage-in-2026-enrollment-update-and-key-trends/</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Health Insurance / Payer</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>ACA insurers seek 10-20% premium increases for 2027 plans</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>Insurers filed proposed 2027 ACA marketplace premiums by the July 15 deadline, with most payers requesting increases in the 10-20% range, setting up another round of affordability debate ahead of open enrollment.</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>Healthcare Dive</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.healthcaredive.com/news/affordable-care-act-premium-increase-2027-kff-peterson-center-healthcare/824695/</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Health Insurance / Payer</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>Express Scripts becomes first major PBM to settle with FTC over insulin pricing practices</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>Cigna's Express Scripts settled FTC allegations that it inflated insulin costs through secretive manufacturer deals, agreeing to eliminate spread pricing and delink compensation from drug list prices ahead of 2027 reforms.</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>HLTH</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>https://hlth.com/insights/articles/the-ftc-just-settled-with-a-pbm-what-s-actually-changing-in-drug-pricing</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Health Insurance / Payer</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>Congress enacts PBM reforms delinking Medicare Part D compensation from drug prices</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>New federal legislation delinks pharmacy benefit manager compensation from drug prices in Medicare Part D, shifting to flat 'bona fide service fees' and prohibiting Medicaid spread pricing under a pass-through model.</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>AJMC</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ajmc.com/view/pbm-reforms-signed-into-law-reshaping-medicare-part-d-drug-pricing-transparency</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Healthcare / Provider &amp; Clinical</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>APAC</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>AI in APAC healthcare enters a new phase in 2026</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>Asia-Pacific health systems are moving beyond pilot-stage AI deployments in 2026, with broader adoption of clinical decision support and imaging tools across the region's hospitals, per Healthcare IT News.</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>Healthcare IT News</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.healthcareitnews.com/news/asia/apac-ai-healthcare-enters-new-phase-2026</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Healthcare / Provider &amp; Clinical</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>27% of health systems now hold commercial AI licenses to ease clinical workload</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>A new survey finds 27% of U.S. health systems have signed commercial AI licenses aimed at reducing clinician workload, part of a broader push to integrate predictive AI tools with electronic health records.</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>PYMNTS</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pymnts.com/artificial-intelligence-2/2026/27percent-health-systems-have-commercial-ai-licenses</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Healthcare / Provider &amp; Clinical</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>Health IT vendors roll out new radiology and nursing documentation AI tools</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>A July 2026 health IT product roundup highlights new AI radiology draft-reporting tools designed to integrate with existing systems without platform migrations, alongside expanded ambient documentation tools for inpatient nursing workflows.</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>Healthcare NOW Radio</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.healthcarenowradio.com/health-it-product-news-report-july-2026/</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Insurtech</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Investments &amp; Funding</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>AI-labeled startups capture record 95.2% of insurtech funding, Gallagher Re finds</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>Global insurtech investment reached $1.63 billion in Q1 2026, up roughly 27% year-over-year, with AI-labeled companies accounting for a record 95.2% share of total funding according to Gallagher Re.</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>Insurance Business Magazine</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.insurancebusinessmag.com/reinsurance/news/breaking-news/ai-startups-capture-record-95-2-of-insurtech-funding--gallagher-re-574376.aspx</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Insurtech</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Investments &amp; Funding</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>Poetic raises $50 million Series A for underwriting and compliance automation</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>Insurtech Poetic secured a $50 million Series A round for its underwriting and compliance automation platform, with investors including Kleiner Perkins, Founders Fund, First Harmonic and OpenAI.</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>Digital Insurance</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dig-in.com/news/top-insurtech-funding-rounds-june-2026</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Insurtech</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Investments &amp; Funding</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>Honeycomb Insurance raises $40 million for digital P&amp;C carrier build-out</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>Digital P&amp;C insurer Honeycomb Insurance raised $40 million from Zeev Ventures, Ibex Investors, Peakline and other investors to expand its underwriting technology and product lines.</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>Digital Insurance</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dig-in.com/news/top-insurtech-funding-rounds-june-2026</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Insurtech</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>AI collapses insurance quote turnaround from days to minutes, industry data shows</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>Industry data cited alongside recent insurtech funding rounds shows AI enabling submission-to-quote timelines to shrink from three days to three minutes and straight-through processing rates to jump from 10-15% to 70-90%.</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>Digital Insurance</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dig-in.com/news/top-insurtech-funding-rounds-june-2026</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Investments &amp; Funding</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>Insurance asset managers hunt for private-market opportunities as credit spreads stay tight</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>With traditional credit spreads historically compressed, insurance asset managers are increasingly diversifying into private markets and alternative assets to sustain investment income, per a Pensions &amp; Investments special report.</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>Pensions &amp; Investments</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pionline.com/institutional-investors/pi-insurance-asset-management-special-report-main-story-2026/</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>UK/Europe</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>AXA balances insurance growth against long-term investment ambitions</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>AXA is weighing continued insurance business expansion against its longer-horizon investment strategy as it navigates a shifting rate and asset-allocation environment.</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>AD-HOC-NEWS</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/axa-balances-insurance-growth-and-long-term-investment-ambitions/69682677</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Investments &amp; Funding</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>Mercer flags top investment considerations for insurers navigating 2026</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>Mercer's 2026 market outlook highlights the investment themes insurers should weigh this year, including rate normalization, private-asset allocation, and portfolio resilience.</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>Mercer</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mercer.com/insights/investments/market-outlook-and-trends/top-investment-considerations-for-insurers/</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>Investments &amp; Funding</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>Mitigata secures $15 million to expand India cyber insurance underwriting</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>India-focused insurtech Mitigata raised $15 million to build out cyber insurance coverage and risk-assessment tools for Indian businesses, part of a broader wave of AI-labeled underwriting funding.</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>Digital Insurance</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dig-in.com/news/top-insurtech-funding-rounds-june-2026</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>Life &amp; Annuities</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>LIMRA projects 2026 U.S. annuity sales to hold above $450 billion after fourth straight record year</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>LIMRA's latest outlook shows retail annuity sales finishing 2025 above $460 billion, with 2026 sales expected to stay above $450 billion as fixed and fixed-indexed products keep gaining share over traditional variable annuities.</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>LIMRA</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.limra.com/en/newsroom/industry-trends/2026/the-2026-annuity-sales-outlook-remains-strong/</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>Life &amp; Annuities</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>Life insurers enter 2026 with strong capital buffers and steady annuity demand</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>InvestmentNews reports life insurers begin 2026 on solid footing, citing robust capital strength and continued consumer demand for annuities as key stabilizers for the sector heading into the year.</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>InvestmentNews</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.investmentnews.com/life-insurance-and-annuities/life-insurers-entered-2026-on-firm-footing-as-capital-strength-and-annuity-demand-hold/265147</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>Life &amp; Annuities</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>APAC</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>PayPay completes purchase of majority stake in T&amp;D Financial Life Insurance</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>Japanese fintech PayPay finalized its acquisition of a 70.2% stake in T&amp;D Financial Life Insurance Company from T&amp;D Holdings, marking a notable fintech entry into life insurance underwriting.</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>SEC EDGAR / PayPay Corp Form 6-K</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/0002080845/000208084526000016/payp-ex99_1.htm</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>Life &amp; Annuities</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>Life and annuity carriers move from AI pilots to permanent transformation in 2026</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>Industry analysis frames 2026 as the year carriers shift from experimenting with AI in underwriting and fraud prevention toward embedding it permanently, even as regulators push for stronger data integrity and cybersecurity standards.</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>InsuranceNewsNet</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>https://insurancenewsnet.com/innarticle/the-forces-shaping-life-and-annuities-in-2026</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>Life &amp; Annuities</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>IRDAI consults industry on insurer-funded policyholder protection fund</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>India's insurance regulator opened a consultation on whether insurers should make ongoing contributions to a new Policyholders' Education and Protection Fund, with industry comments due mid-July.</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>Insurance Business Asia</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.insurancebusinessmag.com/asia/news/breaking-news/irdai-seeks-industry-input-on-insurerfunded-protection-scheme-580814.aspx</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>P&amp;C market enters correction phase with significant property rate relief</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>The U.S. property and casualty market is softening, with a quieter-than-expected 2025 hurricane season and record reinsurance capital driving rate decreases of 10-30% on shared and layered placements versus expiring terms.</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>Risk &amp; Insurance</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>https://riskandinsurance.com/pc-market-enters-correction-phase-with-significant-rate-relief-and-emerging-challenges/</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>APAC</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>Fitch keeps APAC insurance outlook neutral for 2026 despite rising claims costs</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>Fitch Ratings maintained a neutral 2026 outlook for Asia-Pacific insurers, citing capital buffers and disciplined underwriting offsetting rising claims costs, with non-life premium growth forecast at 2.5%.</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>InsuranceAsiaNews</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>https://insuranceasianews.com/apac-insurance-outlook-neutral-for-2026-despite-rising-claims-cost-fitch/</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>People &amp; Leadership</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>Kellen Booher named President &amp; CEO of CopperPoint Insurance</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>CopperPoint Insurance named Kellen Booher as its new President and CEO, a leadership transition for the workers' compensation-focused P&amp;C carrier.</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/kellen-booher-named-president--ceo-of-copperpoint-insurance-302731454.html</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>People &amp; Leadership</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>Progressive CFO to step down in July 2026 after a decade in the role</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>Progressive's long-serving CFO is set to step down in July 2026, capping roughly 35 years with the auto and property insurer including a decade as chief financial officer.</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>Life Insurance International</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lifeinsuranceinternational.com/news/progressive-cfo-step-down-july-2026/</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>India raises insurer penalties tenfold under new insurance law amendments</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>The maximum penalty for violations of India's Insurance Act and IRDAI Act increased tenfold, from ₹1 crore to ₹10 crore, under the newly enacted Sabka Bima Sabki Raksha (Amendment of Insurance Laws) Act.</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.business-standard.com/amp/finance/insurance/irdai-proposes-framework-for-regulation-making-public-consultations-126061701305_1.html</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>Retirement</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>Human Interest to take over 401(k) recordkeeping for UBS</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>Human Interest will provide 401(k) recordkeeping services for UBS, using automated workflows integrated with over 500 payroll providers to track ACH debits, contribution flows, and funding status.</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>401(k) Specialist</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>https://401kspecialistmag.com/human-interest-to-provide-recordkeeping-for-ubs/</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>Retirement</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>Early look at 'How America Saves' 2026 points to record 401(k) balances on auto-enrollment strength</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>A preview of Vanguard's forthcoming How America Saves 2026 report suggests automatic enrollment and auto-escalation features are pushing account balances to new highs despite market volatility.</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>401(k) Specialist</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>https://401kspecialistmag.com/how-america-saves-2026-preview-strong-market-auto-features-power-record-401k-balances/</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>Retirement</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>2026 contribution limits rise to $24,500 for 401(k)-style plans</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>The 2026 contribution limit for workers under 50 in job-based retirement accounts rose to $24,500, while workers aged 50-59 and 64-plus gained an $8,000 catch-up allowance, up from $7,500 in 2025.</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>AARP</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aarp.org/money/retirement/biggest-changes-2026/</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>Retirement</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>UK/Europe</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>UK pension risk transfer market on pace for record £70 billion in 2026</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>Forecasts show the amount of UK defined-benefit pension risk transferred to insurers climbing roughly 15% in 2026 to about £70 billion, with the bulk annuity segment alone expected to top £50 billion for the first time.</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>Employee Benefits</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>https://employeebenefits.co.uk/pensions/pension-risk-transfer-market-forecast-to-reach-70-billion-in-2026/281865.article</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>Retirement</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>US pension risk transfer sales slipped to $49 billion in 2025 even as buy-in deals grew</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>US pension risk transfer sales fell 6% year-over-year to $49 billion in 2025, but insurers report the buy-in segment kept expanding and expect that trend to continue through 2026.</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>Pensions &amp; Investments</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pionline.com/institutional-investors/pension-risk-transfer/pi-pension-risk-transfer-2026-outlook-lawsuits/</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>TPA</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Insurance launches AI-native third-party administrator Corgi Claims</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Insurance launched Corgi Claims, a full-service TPA pairing a nationwide network of more than 5,000 licensed adjusters with AI that reviews every claim on report, scoring severity and flagging coverage issues and missing documents.</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/corgi-insurance-launches-corgi-claims-the-ai-native-tpa-302813039.html</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>TPA</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>Global insurance TPA market revenue grows by $32 billion year-over-year</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>A new market report finds the insurance third-party administrator sector's global revenue expanded by roughly $32 billion year-over-year, with AI-driven claims automation cited as a key growth driver through 2030.</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>GlobeNewswire</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2026/04/27/3281499/0/en/insurance-third-party-administrators-tpas-global-market-report-2026-yoy-revenue-grew-by-32-billion-ai-driven-claims-automation-to-boost-insurance-tpa-growth-through-2030.html</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Management</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>RIA M&amp;A hits record $1.67 trillion in deal value in Q1 2026</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>Echelon Partners reports RIA merger-and-acquisition activity reached a new quarterly record in Q1 2026, with $1.67 trillion in cumulative deal value as consolidation among registered investment advisors accelerates.</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>InvestmentNews</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.investmentnews.com/ria-news/ria-ma-hits-new-quarterly-record-in-q1-2026-with-167-trillion-in-deals/266421</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Management</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>Choreo continues acquisition run, adding Illinois-based RIA</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>Choreo acquired an Illinois registered investment advisor as part of a string of 2026 deals under new CEO Jason Van de Loo, adding roughly $2 billion in combined assets under management this year.</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>WealthManagement.com</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wealthmanagement.com/ria-news/choreo-acquires-illinois-ria-with-700m-in-assets</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Management</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>Wealthtech roundup: AI-native platforms and prospecting tools gain traction among large RIAs</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>A weekly wealthtech roundup covers AI-native wealth manager Arca raising $64 million with backing from Vanguard's former CEO, and a $17 billion RIA naming a money-in-motion prospecting platform as its enterprise-wide tool.</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>WealthTech Strategy</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wealthtechstrategy.com/post/the-wealthtech-safari-week-of-july-3-2026</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Management</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>Citi Wealth rolls out AI tools including AskWealth CIO and CitiScribe for advisors</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F198" s="2" t="inlineStr">
         <is>
           <t>Citi Wealth unveiled new advisor-facing AI capabilities such as Portfolio Intelligence, AskWealth CIO, Client 360 and CitiScribe, aimed at delivering more data-driven, personalized client experiences.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G198" s="2" t="inlineStr">
         <is>
           <t>Citigroup</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H198" s="2" t="inlineStr">
         <is>
           <t>https://www.citigroup.com/global/news/press-release/2026/citi-wealth-deploys-ai-powered-technology-to-enhance-client-experience</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="I198" s="2" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>

--- a/cockpit-data/story-log-last30days.xlsx
+++ b/cockpit-data/story-log-last30days.xlsx
@@ -10,7 +10,9 @@
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Raw Rows (Last 30 Days)" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw Rows (Last 30 Days)'!$A$1:$I$229</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -58,6 +60,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00004B87"/>
+        <bgColor rgb="00004B87"/>
       </patternFill>
     </fill>
   </fills>
@@ -444,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -461,7 +464,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Window: 2026-06-08 to 2026-07-08</t>
+          <t>Window: 2026-06-22 to 2026-07-22</t>
         </is>
       </c>
     </row>
@@ -491,7 +494,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -501,7 +504,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +514,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -521,27 +524,27 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Insurtech</t>
+          <t>Healthcare / Provider &amp; Clinical</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Healthcare / Provider &amp; Clinical</t>
+          <t>Insurtech</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -551,7 +554,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -561,37 +564,37 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Investments</t>
+          <t>BrokerTech</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>BrokerTech</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Investments</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -601,7 +604,7 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -630,7 +633,7 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23">
@@ -640,7 +643,7 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24">
@@ -650,7 +653,7 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25">
@@ -660,7 +663,7 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26">
@@ -670,7 +673,7 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27">
@@ -680,7 +683,7 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30">
@@ -720,6 +723,16 @@
       </c>
       <c r="B33" s="2" t="n">
         <v>79</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-W30</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -733,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I198"/>
+  <dimension ref="A1:I229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10053,7 +10066,1465 @@
         </is>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>BrokerTech</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>Vertafore rolls out new AI agents to automate carrier statement reconciliation for agencies</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>Vertafore released two new Velocity AI agents inside its AgencyOne platform that automate carrier statement reconciliation and turn Outlook email activity into structured workflows, aiming to cut manual work for independent insurance agencies.</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/vertafores-latest-ai-innovations-help-agencies-accelerate-carrier-statement-reconciliation-and-turn-outlook-activity-into-structured-workflows-302813535.html</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>BrokerTech</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>People &amp; Leadership</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>Fulcrum taps veteran brokerage operations executive to drive AI workflow push</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>Broker-facing AI automation platform Fulcrum brought on a brokerage operations veteran to lead its push into deeper AI workflow adoption, following the company's recent $25 million funding round.</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>Insurance Business America</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.insurancebusinessmag.com/us/news/breaking-news/fulcrum-taps-brokerage-ops-veteran-to-drive-ai-workflow-push-575702.aspx</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>Brokers &amp; MGA/GA</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>Arrow Global Insurance acquires MGA Fusion Specialty Group</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>Arrow Global Insurance agreed to acquire managing general agent Fusion Specialty Group, a deal expected to close in the third quarter of 2026 pending regulatory approval, expanding Arrow's specialty program footprint.</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>The Insurer</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theinsurer.com/program-manager/news/arrow-global-insurance-acquires-mga-fusion-specialty-group-2026-07-09/</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>Brokers &amp; MGA/GA</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>Investments &amp; Funding</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>American Growth Insurance raises $70 million to acquire and rebuild US brokerages with AI</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>Tech-forward brokerage growth platform American Growth Insurance raised $70 million in committed equity led by Atomic and Rockbridge Growth Equity, aiming to close several more independent agency acquisitions and rebuild their operations around AI agents.</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>Beinsure</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>https://beinsure.com/news/american-growth-insurance-raised-70mn/</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>Brokers &amp; MGA/GA</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>People &amp; Leadership</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>UK/Europe</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>PIB Group names Alastair Hay as chief financial officer</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>UK-based insurance intermediary PIB Group appointed Alastair Hay as its new chief financial officer effective immediately, part of a wave of senior leadership moves across European brokers and MGAs in mid-July.</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>Insurance Edge</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>https://insurance-edge.net/2026/07/13/job-moves-and-senior-appointments-13-07-2026/</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>FinTech</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>One Inc and CalcFocus team up to modernize life insurance premium payments</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>Payments network One Inc partnered with policy administration provider CalcFocus to integrate its PremiumPay platform, letting life insurers offer policyholders Apple Pay, Google Pay, PayPal and Venmo alongside traditional card payments.</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>FinTech Global</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>https://fintech.global/2026/07/17/one-inc-and-calcfocus-target-friction-in-life-insurance-pay/</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>FinTech</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>Investments &amp; Funding</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>Fulcrum raises $25 million to scale AI automation across US insurance brokers</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>Fulcrum raised $25 million in seed and Series A funding led by CRV to expand its AI platform for insurance brokers, which automates proposal creation, policy checks and coverage comparisons and has cut policy delivery timelines from 15 days to same-day.</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>Beinsure</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>https://beinsure.com/news/fulcrum-raises-25mn-led-by-crv/</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>FinTech</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>PropTech firm Foxen embeds Healthy Paws pet insurance into its renter platform</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>Foxen partnered with pet insurer Healthy Paws to embed discounted pet coverage directly into its PetClear renter platform, giving qualifying residents a 5% savings on new policies as embedded insurance keeps expanding beyond core financial products.</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>FinTech Global</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>https://fintech.global/2026/07/16/foxen-teams-with-healthy-paws-on-renter-pet-insurance/</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>Health Insurance / Payer</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>UnitedHealth Group's Q2 profit hits $5.4 billion as medical costs ease</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>UnitedHealth Group reported second-quarter net income of $5.48 billion and raised its 2026 earnings forecast after its medical care ratio fell to 86.7% from 89.4% a year earlier, aided by benefit redesign and exits from unprofitable ACA and Medicare Advantage markets.</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>Forbes</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.forbes.com/sites/brucejapsen/2026/07/16/unitedhealth-group-profits-hit-54-billion-as-costs-continue-to-ease/</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>Health Insurance / Payer</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>FTC secures Caremark settlement locking in up to $8.5 billion in consumer drug savings</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>The Federal Trade Commission reached a settlement with Caremark Rx and Zinc Health Services resolving claims that the PBM used anticompetitive rebate schemes to inflate insulin prices, requiring rebate pass-through at the point of sale and estimated to save consumers up to $8.5 billion over a decade.</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>Managed Healthcare Executive</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.managedhealthcareexecutive.com/view/ftc-secures-settlement-with-caremark-locks-in-up-to-8-5-billion-in-consumer-savings</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>Health Insurance / Payer</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>Health insurers propose median 14% premium increases across ACA exchanges for 2027</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>Insurers in 16 states and Washington, D.C. have proposed a median 14% premium increase for next year's ACA exchange plans, citing rising healthcare costs and the scheduled expiration of enhanced federal subsidies.</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>NOTUS</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.notus.org/healthcare/health-insurers-are-proposing-to-increase-premiums-again</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>Healthcare / Provider &amp; Clinical</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>Sutter Health and Allina Health sign definitive deal to form $26 billion nonprofit system</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>Sacramento-based Sutter Health signed a definitive agreement to acquire Minneapolis-based Allina Health, creating a combined 39-hospital, $26 billion nonprofit system spanning California, Minnesota and Wisconsin, with Sutter committing $2 billion to Allina's home markets.</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>Fierce Healthcare</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fiercehealthcare.com/providers/allina-health-join-sutter-health-26b-proposed-merger</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>Healthcare / Provider &amp; Clinical</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>Clinical-grade AI moves from data center to point of care as governance infrastructure catches up</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>A July 2026 digital health roundup finds clinical AI increasingly deployed at the point of care through surgical robots and wearables, with health system leaders emphasizing that strong oversight and clinician accountability determine whether AI strengthens or undermines patient trust.</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>MarketScale</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.marketscale.com/industries/healthcare/digital-healths-july-2026-signal-ai-wearables-a-new-cms-office-and-the-telehealth-billing-fight</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>Insurtech</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>Investments &amp; Funding</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>Cover Genius raises $100 million credit facility at $1.9 billion valuation</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>Embedded insurance platform Cover Genius closed a $100 million credit raise backed by Vista Credit Partners at a $1.9 billion valuation, a sign that embedded insurance financing has matured beyond traditional venture capital rounds.</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>Tech Times</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.techtimes.com/articles/320689/20260716/cover-genius-100m-raise-signals-embedded-insurance-has-outgrown-venture-capital.htm</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>Insurtech</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>Bamboo Insurance unveils Essential homeowners coverage for straightforward risks</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>Technology-enabled managing general underwriter Bamboo Insurance launched its Essential homeowners program, an HO2 product built around core coverage for buyers seeking simpler, more affordable protection.</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>FinTech Global</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>https://fintech.global/2026/07/06/bamboo-insurance-unveils-essential-homeowners-cover/</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>P&amp;C insurers' book yields hit decade high in 2025 even as income growth cools</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>Property-casualty insurers' portfolio book yield climbed to a ten-year high of 4.39% in 2025, though net investment income as a share of invested assets slipped modestly from its 2024 peak as reinvestment rates began to normalize.</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>NEAM</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.neamgroup.com/insights/2025-pc-industry-investment-highlights-elevated-yields-persist-as-income-growth-moderates</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>Global insurer invested assets climb to $9.6 trillion as insurers keep pivoting toward private markets</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>A Goldman Sachs Asset Management survey finds US insurers' cash and invested assets grew 6.7% year-over-year to $9.6 trillion at the end of 2025, with respondents expecting continued rotation into private credit and asset-backed finance for incremental yield.</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>Goldman Sachs Asset Management</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>https://am.gs.com/en-us/advisors/insights/report-survey/global-insurance-survey</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>Life &amp; Annuities</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>Indexed annuity trade group pushes back on proposed illustration rule changes</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>The Indexed Annuity Leadership Council submitted comments to the NAIC's Life Insurance and Annuities Illustrations working group opposing parts of a proposed overhaul of Model #245, the annuity disclosure regulation, ahead of further working-group review.</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>NAIC</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>https://content.naic.org/sites/default/files/inline-files/ialc-comment.pdf</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>Life &amp; Annuities</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>Life insurers head into second half of 2026 favoring quiet block and reinsurance deals over big mergers</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>Industry analysts expect life and annuity M&amp;A to stay measured through the rest of 2026, with closed-block transactions, reinsurance arrangements and distribution-driven deals dominating rather than large-scale carrier mergers.</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P Global Market Intelligence</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>https://www.spglobal.com/market-intelligence/en/news-insights/articles/2026/1/us-life-insurance-2026-outlook-more-closed-block-deals-plenty-of-upside-96755623</t>
+        </is>
+      </c>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>Property reinsurance rates fall as much as 25% at July renewals on record capital</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>Abundant reinsurance capital pushed property catastrophe rates down as much as 25% at the July 1 renewal, with Guy Carpenter's global property rate-on-line index posting its steepest annual decline since the late 1990s.</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>Business Insurance</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.businessinsurance.com/reinsurance-property-renewal-rates-dive-as-much-as-25/</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>US commercial insurance buyers see relief in property and cyber, but casualty costs keep climbing</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>Alliant's midyear market report finds US commercial buyers getting rate relief in property and cyber lines, while casualty and transportation risks remain pressured by litigation costs and rising claims severity.</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>The Insurer</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theinsurer.com/ti/news/us-insurance-buyers-see-relief-in-property-cyber-but-casualty-costs-keep-2026-07-20/</t>
+        </is>
+      </c>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>APAC</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>KKR joins consortium's A$7.7 billion bid to take Australian broker Steadfast private</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>KKR joined Amwins Group and Dragoneer Investment Group's non-binding proposal to acquire Australian insurance broker Steadfast Group for roughly A$7.7 billion, with KKR and Dragoneer set to control the retail brokerage business and Amwins taking the underwriting agency operations.</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>The Insurer</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theinsurer.com/ti/news/kkr-joins-amwins-dragoneer-consortium-bidding-to-acquire-steadfast-2026-07-14/</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>Excess and surplus lines property rate softening accelerates as casualty increases slow</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>CRC Group's REDY report shows property rate softening picking up pace in the excess and surplus market even as the rate of casualty rate increases begins to decelerate, reflecting the broader bifurcation in the US commercial market.</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>The Insurer</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theinsurer.com/e-and-s/news/crc-redy-property-rate-softening-accelerates-as-excess-casualty-increases-slow-2026-07-16/</t>
+        </is>
+      </c>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>Retirement</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>India's EPFO formally launches overhauled EPF, pension and insurance schemes for 2026</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>EPFO rolled out its restructured EPF, EPS and EDLI schemes for 2026 effective July 1, keeping contribution rates unchanged while crediting 8.25% interest on provident fund balances and raising the auto-settlement claims limit to ₹5 lakh.</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>Business Today</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.businesstoday.in/personal-finance/news/story/epfos-new-eps-2026-is-here-whats-changed-for-pensioners-and-epf-subscribers-540351-2026-07-02</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>Retirement</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>UK/Europe</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;G completes £760 million bulk annuity deal, closing out UK pension scheme's buy-in program</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;G finalized a £760 million bulk purchase annuity with the Smiths Industries Pension Scheme covering more than 10,000 members, the scheme's fifth and final buy-in as UK insurers keep absorbing defined-benefit pension risk.</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>Insurance Edge</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>https://insurance-edge.net/2026/07/21/mg-completes-760m-bulk-purchase-annuity-deal/</t>
+        </is>
+      </c>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>Retirement</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>US pension risk transfer deals grow in number but shrink in size as funding surpluses persist</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>LIMRA data shows the first half of 2026 was marked by a rising count of smaller defined-benefit buy-in transactions even as total US pension risk transfer deal volume edged lower, with insurers still expecting strong appetite for the rest of the year.</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>Pensions &amp; Investments</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pionline.com/institutional-investors/pension-risk-transfer/pi-limra-pension-risk-transfer-july-2026/</t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>TPA</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>Insurance TPA and claims-services businesses fetch 4x-8x EBITDA in 2026 deal market</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>A new valuation analysis finds founder-led insurance third-party administrator and claims-services firms transacting between 4x and 8x EBITDA in 2026, with revenue type, client concentration and workforce structure driving where deals land in that range.</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>CT Acquisitions</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>https://ctacquisitions.com/guides/insurance-tpa-business-valuation/</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Management</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Enhancement expands Houston footprint with $299 million Trippon acquisition</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Enhancement closed its purchase of Trippon Wealth Management Group and its affiliated CPA practice, adding roughly $299 million in client assets and pushing the RIA aggregator past $158 billion in total client assets.</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>InvestmentNews</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.investmentnews.com/ria-news/wealth-enhancement-expands-houston-footprint-with-trippon-acquisition/267440</t>
+        </is>
+      </c>
+      <c r="I226" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Management</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>Creative Planning bolsters commercial insurance arm with Lovell Insurance Group deal</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>Creative Planning, a roughly $710 billion RIA, acquired Lee's Summit, Missouri-based commercial insurance brokerage Lovell Insurance Group, continuing a run of specialized acquisitions meant to bring risk-management services to its wealth clients.</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>InvestmentNews</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.investmentnews.com/ria-news/creative-planning-bolsters-commercial-insurance-arm-with-lovell-deal/267443</t>
+        </is>
+      </c>
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Management</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>Investments &amp; Funding</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>Wealth fintech Arca emerges from stealth with $64 million to build AI-powered advisory platform</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>Arca, founded by a former Plaid product lead, raised a combined $64 million seed and Series A round led by Venrock and General Catalyst to build AI agents meant to support human financial advisors across planning, tax and estate work.</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>The AI Insider</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>https://theaiinsider.tech/2026/07/13/wealth-management-fintech-arca-emerges-from-stealth-with-64-million-to-build-ai-powered-advisory-platform/</t>
+        </is>
+      </c>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>Wealth Management</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>US wealthtech deal count jumps 27% in Q2 2026 even as total funding declines</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>US wealthtech recorded 116 deals in the second quarter of 2026, up 27% year-over-year, even though total funding fell 41% to $557.8 million as investors favored more, smaller rounds over mega-deals.</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>FinTech Global</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>https://fintech.global/2026/07/16/california-emerged-as-the-main-us-wealthtech-hub-in-q2-as-deal-activity-grew-by-27-yoy/</t>
+        </is>
+      </c>
+      <c r="I229" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:I229"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cockpit-data/story-log-last30days.xlsx
+++ b/cockpit-data/story-log-last30days.xlsx
@@ -46798,9 +46798,8 @@
           <t>Health Insurance / Payer</t>
         </is>
       </c>
-      <c r="B3" s="6">
-        <f>COUNTIF('Raw Rows'!B2:B890,A3)</f>
-        <v/>
+      <c r="B3" s="6" t="n">
+        <v>102</v>
       </c>
     </row>
     <row r="4">
@@ -46809,9 +46808,8 @@
           <t>Healthcare / Provider &amp; Clinical</t>
         </is>
       </c>
-      <c r="B4" s="6">
-        <f>COUNTIF('Raw Rows'!B2:B890,A4)</f>
-        <v/>
+      <c r="B4" s="6" t="n">
+        <v>101</v>
       </c>
     </row>
     <row r="5">
@@ -46820,9 +46818,8 @@
           <t>Property &amp; Casualty</t>
         </is>
       </c>
-      <c r="B5" s="6">
-        <f>COUNTIF('Raw Rows'!B2:B890,A5)</f>
-        <v/>
+      <c r="B5" s="6" t="n">
+        <v>91</v>
       </c>
     </row>
     <row r="6">
@@ -46831,9 +46828,8 @@
           <t>Wealth Management</t>
         </is>
       </c>
-      <c r="B6" s="6">
-        <f>COUNTIF('Raw Rows'!B2:B890,A6)</f>
-        <v/>
+      <c r="B6" s="6" t="n">
+        <v>86</v>
       </c>
     </row>
     <row r="7">
@@ -46842,9 +46838,8 @@
           <t>Brokers &amp; MGA/GA</t>
         </is>
       </c>
-      <c r="B7" s="6">
-        <f>COUNTIF('Raw Rows'!B2:B890,A7)</f>
-        <v/>
+      <c r="B7" s="6" t="n">
+        <v>83</v>
       </c>
     </row>
     <row r="8">
@@ -46853,9 +46848,8 @@
           <t>Life &amp; Annuities</t>
         </is>
       </c>
-      <c r="B8" s="6">
-        <f>COUNTIF('Raw Rows'!B2:B890,A8)</f>
-        <v/>
+      <c r="B8" s="6" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="9">
@@ -46864,9 +46858,8 @@
           <t>Insurtech</t>
         </is>
       </c>
-      <c r="B9" s="6">
-        <f>COUNTIF('Raw Rows'!B2:B890,A9)</f>
-        <v/>
+      <c r="B9" s="6" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="10">
@@ -46875,9 +46868,8 @@
           <t>Investments</t>
         </is>
       </c>
-      <c r="B10" s="6">
-        <f>COUNTIF('Raw Rows'!B2:B890,A10)</f>
-        <v/>
+      <c r="B10" s="6" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="11">
@@ -46886,9 +46878,8 @@
           <t>Retirement</t>
         </is>
       </c>
-      <c r="B11" s="6">
-        <f>COUNTIF('Raw Rows'!B2:B890,A11)</f>
-        <v/>
+      <c r="B11" s="6" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="12">
@@ -46897,9 +46888,8 @@
           <t>BrokerTech</t>
         </is>
       </c>
-      <c r="B12" s="6">
-        <f>COUNTIF('Raw Rows'!B2:B890,A12)</f>
-        <v/>
+      <c r="B12" s="6" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="13">
@@ -46908,9 +46898,8 @@
           <t>FinTech</t>
         </is>
       </c>
-      <c r="B13" s="6">
-        <f>COUNTIF('Raw Rows'!B2:B890,A13)</f>
-        <v/>
+      <c r="B13" s="6" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="14">
@@ -46919,9 +46908,8 @@
           <t>TPA</t>
         </is>
       </c>
-      <c r="B14" s="6">
-        <f>COUNTIF('Raw Rows'!B2:B890,A14)</f>
-        <v/>
+      <c r="B14" s="6" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="16">
@@ -46949,9 +46937,8 @@
           <t>Market Economics</t>
         </is>
       </c>
-      <c r="B18" s="6">
-        <f>COUNTIF('Raw Rows'!C2:C890,A18)</f>
-        <v/>
+      <c r="B18" s="6" t="n">
+        <v>231</v>
       </c>
     </row>
     <row r="19">
@@ -46960,9 +46947,8 @@
           <t>M&amp;A</t>
         </is>
       </c>
-      <c r="B19" s="6">
-        <f>COUNTIF('Raw Rows'!C2:C890,A19)</f>
-        <v/>
+      <c r="B19" s="6" t="n">
+        <v>151</v>
       </c>
     </row>
     <row r="20">
@@ -46971,9 +46957,8 @@
           <t>Technology &amp; AI</t>
         </is>
       </c>
-      <c r="B20" s="6">
-        <f>COUNTIF('Raw Rows'!C2:C890,A20)</f>
-        <v/>
+      <c r="B20" s="6" t="n">
+        <v>151</v>
       </c>
     </row>
     <row r="21">
@@ -46982,9 +46967,8 @@
           <t>Regulatory &amp; Policy</t>
         </is>
       </c>
-      <c r="B21" s="6">
-        <f>COUNTIF('Raw Rows'!C2:C890,A21)</f>
-        <v/>
+      <c r="B21" s="6" t="n">
+        <v>143</v>
       </c>
     </row>
     <row r="22">
@@ -46993,9 +46977,8 @@
           <t>Investments &amp; Funding</t>
         </is>
       </c>
-      <c r="B22" s="6">
-        <f>COUNTIF('Raw Rows'!C2:C890,A22)</f>
-        <v/>
+      <c r="B22" s="6" t="n">
+        <v>108</v>
       </c>
     </row>
     <row r="23">
@@ -47004,9 +46987,8 @@
           <t>People &amp; Leadership</t>
         </is>
       </c>
-      <c r="B23" s="6">
-        <f>COUNTIF('Raw Rows'!C2:C890,A23)</f>
-        <v/>
+      <c r="B23" s="6" t="n">
+        <v>105</v>
       </c>
     </row>
     <row r="25">
@@ -47034,9 +47016,8 @@
           <t>2026-W27</t>
         </is>
       </c>
-      <c r="B27" s="6">
-        <f>COUNTIF('Raw Rows'!J2:J890,A27)</f>
-        <v/>
+      <c r="B27" s="6" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="28">
@@ -47045,9 +47026,8 @@
           <t>2026-W28</t>
         </is>
       </c>
-      <c r="B28" s="6">
-        <f>COUNTIF('Raw Rows'!J2:J890,A28)</f>
-        <v/>
+      <c r="B28" s="6" t="n">
+        <v>275</v>
       </c>
     </row>
     <row r="29">
@@ -47056,9 +47036,8 @@
           <t>2026-W29</t>
         </is>
       </c>
-      <c r="B29" s="6">
-        <f>COUNTIF('Raw Rows'!J2:J890,A29)</f>
-        <v/>
+      <c r="B29" s="6" t="n">
+        <v>197</v>
       </c>
     </row>
     <row r="30">
@@ -47067,9 +47046,8 @@
           <t>2026-W30</t>
         </is>
       </c>
-      <c r="B30" s="6">
-        <f>COUNTIF('Raw Rows'!J2:J890,A30)</f>
-        <v/>
+      <c r="B30" s="6" t="n">
+        <v>174</v>
       </c>
     </row>
     <row r="31">
@@ -47078,9 +47056,8 @@
           <t>2026-W31</t>
         </is>
       </c>
-      <c r="B31" s="6">
-        <f>COUNTIF('Raw Rows'!J2:J890,A31)</f>
-        <v/>
+      <c r="B31" s="6" t="n">
+        <v>163</v>
       </c>
     </row>
     <row r="32">
@@ -47089,9 +47066,8 @@
           <t>2026-W32</t>
         </is>
       </c>
-      <c r="B32" s="6">
-        <f>COUNTIF('Raw Rows'!J2:J890,A32)</f>
-        <v/>
+      <c r="B32" s="6" t="n">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/cockpit-data/story-log-last30days.xlsx
+++ b/cockpit-data/story-log-last30days.xlsx
@@ -29,20 +29,31 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001A2E40"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="0000294D"/>
       <sz val="16"/>
     </font>
     <font>
       <name val="Arial"/>
       <i val="1"/>
-      <color rgb="007A8FA3"/>
-      <sz val="9"/>
+      <color rgb="004A5E72"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <i val="1"/>
-      <color rgb="004A5E72"/>
-      <sz val="10"/>
+      <color rgb="007A8FA3"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -53,18 +64,8 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <color rgb="001A2E40"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="001A2E40"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="3">
@@ -80,7 +81,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -88,38 +89,19 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00D0D7E0"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D0D7E0"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D0D7E0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D0D7E0"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -485,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C46"/>
+  <dimension ref="B2:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -503,7 +485,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Window: 2026-07-14 to 2026-08-13  |  Generated: 2026-08-13  |  Rows in window: 27</t>
+          <t>Window: 2026-07-16 to 2026-08-14  |  Generated: 2026-08-14  |  Rows in window: 50</t>
         </is>
       </c>
     </row>
@@ -514,109 +496,99 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="4" t="inlineStr">
+    <row r="6">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Counts by Vertical</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="5" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Vertical</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Stories</t>
         </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>BrokerTech</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Brokers &amp; MGA/GA</t>
+          <t>BrokerTech</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Brokers &amp; MGA/GA</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Health Insurance / Payer</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Healthcare / Provider &amp; Clinical</t>
+          <t>Health Insurance / Payer</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Insurtech</t>
+          <t>Healthcare / Provider &amp; Clinical</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Investments</t>
+          <t>Insurtech</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Life &amp; Annuities</t>
+          <t>Investments</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty</t>
+          <t>Life &amp; Annuities</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
@@ -626,248 +598,258 @@
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Retirement</t>
+          <t>Property &amp; Casualty</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>Retirement</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
+          <t>TPA</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="6" t="inlineStr">
+        <is>
           <t>Wealth Management</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="4" t="inlineStr">
+      <c r="C19" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C19" s="4" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="4" t="inlineStr">
+      <c r="C20" s="7" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Counts by Lens</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Lens</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Stories</t>
         </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>Investments &amp; Funding</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>M&amp;A</t>
+          <t>Investments &amp; Funding</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Market Economics</t>
+          <t>M&amp;A</t>
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>People &amp; Leadership</t>
+          <t>Market Economics</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Regulatory &amp; Policy</t>
+          <t>People &amp; Leadership</t>
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="6" t="inlineStr">
         <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="6" t="inlineStr">
+        <is>
           <t>Technology &amp; AI</t>
         </is>
       </c>
-      <c r="C29" s="6" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="4" t="inlineStr">
+      <c r="C30" s="6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C30" s="4" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="4" t="inlineStr">
+      <c r="C31" s="7" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>Counts by Geography</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="5" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Geography</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Stories</t>
         </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>APAC</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>APAC</t>
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>UK/Europe</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="6" t="inlineStr">
         <is>
+          <t>UK/Europe</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="6" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="C39" s="6" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="4" t="inlineStr">
+      <c r="C40" s="6" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C40" s="4" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="4" t="inlineStr">
+      <c r="C41" s="7" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>Counts by Week (date_added, ISO week)</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>ISO Week</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>Stories</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="6" t="inlineStr">
+    <row r="46">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>2026-W33</t>
         </is>
       </c>
-      <c r="C45" s="6" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="4" t="inlineStr">
+      <c r="C46" s="6" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C46" s="4" t="n">
-        <v>27</v>
+      <c r="C47" s="7" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -881,17 +863,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -943,1271 +925,2352 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Life &amp; Annuities</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>M&amp;A</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>APAC</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>Allianz to buy HSBC Life Singapore for roughly $2bn, locks in 15-year bancassurance tie-up</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Allianz agreed to acquire HSBC Life Singapore for about S$2.7 billion and signed a 15-year exclusive distribution partnership with HSBC Singapore, deepening its foothold in one of Asia's wealthiest insurance markets.</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>Allianz</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>https://www.allianz.com/en/mediacenter/news/media-releases/financials/260724-allianz-to-acquire-hsbc-life-singapore-and-enter-a-new-long-term-distribution-partnership-with-hsbc-singapore.html</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Life &amp; Annuities</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Market Economics</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>LIC's quarterly profit jumps 23% as new-business margins widen sharply</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>State-run insurer LIC reported a 23% year-on-year rise in first-quarter net profit to roughly Rs 13,492 crore, with value of new business surging 61% and margins expanding nearly 750 basis points.</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>APAC News Network</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>https://apacnewsnetwork.com/2026/08/lic-q1-results-net-profit-jumps-23-percent-to-13492-crore/</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Retirement</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>M&amp;A</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>UK/Europe</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Standard Life to buy Aegon UK for GBP2bn, creating the UK's largest retirement savings business</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Standard Life agreed to acquire Aegon's UK pensions and savings arm in a GBP2 billion deal, forming a combined retirement business serving 16 million customers with roughly GBP480 billion in assets under administration.</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Professional Pensions</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>https://www.professionalpensions.com/news/4528312/standard-life-buys-aegon-uk-2bn</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Retirement</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Technology &amp; AI</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Retirement Clearinghouse pitches centralized system to fix 401(k) rollover fragmentation</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Retirement Clearinghouse proposed a centralized clearinghouse to address fragmentation in the defined-contribution system, aiming to make it easier for savers to consolidate small accounts when they change jobs or roll into an IRA.</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>WealthManagement.com</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>https://www.wealthmanagement.com/rpa-news/rch-proposes-radical-system-intervention-for-401-k-plans</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Retirement</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Regulatory &amp; Policy</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Neal and Wyden introduce bill cracking down on outsized 'mega' retirement accounts</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>House Ways and Means Ranking Member Richard Neal and Senator Ron Wyden introduced legislation aimed at curbing unusually large IRA and retirement-account balances, part of a broader push on retirement-savings fairness.</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Office of Rep. Richard Neal</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>https://neal.house.gov/2026/07/22/neal-wyden-introduce-bill-to-crack-down-on-mega-retirement-accounts/</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Investments</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Technology &amp; AI</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Fidelity to add a guaranteed-income option to its target-date fund lineup</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Fidelity plans to launch Freedom Lifetime, a suite of target-date collective investment trusts with a built-in guaranteed-income feature backed by insurers including Nationwide and New York Life, available to plan sponsors in early 2027.</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Fidelity Investments</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>https://newsroom.fidelity.com/pressreleases/fidelity-investments--to-expand-target-date-lineup-with-launch-of-guaranteed-income-solution/s/afb7c7fe-f18f-4727-8aa5-3750a24cf9e0</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Investments</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Market Economics</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>Guaranteed-income assets embedded in target-date funds top $100 billion</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Assets tied to guaranteed-income features within target-date funds reached about $103 billion, up 25% from year-end 2024, as more insurers and asset managers partner on in-plan lifetime-income products.</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>401(k) Specialist</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>https://401kspecialistmag.com/guaranteed-income-features-in-target-dates-exceed-100b/</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Wealth Management</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>M&amp;A</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>Carlyle and Bain wage bidding war for $160bn RIA Wealth Enhancement</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Private equity firms Carlyle and Bain Capital are reportedly competing to acquire mega-RIA Wealth Enhancement, which manages roughly $160 billion in client assets, in a deal said to be worth about $7 billion including debt.</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>InvestmentNews</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>https://www.investmentnews.com/ria-news/private-equity-bidding-war-targets-160bn-ria-in-7bn-deal/267559</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Property &amp; Casualty</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>Regulatory &amp; Policy</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>Allstate seeks Illinois homeowners rate hikes up to 10.4% as losses mount</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Allstate filed for new homeowners rate increases of up to 10.4% affecting more than 200,000 Illinois policyholders, citing severe weather and rising repair costs, reigniting debate over state rate-oversight rules.</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>AM Best / BestWire</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>https://news.ambest.com/newscontent.aspx?AltSrc=23&amp;RefNum=271720</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Property &amp; Casualty</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>M&amp;A</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Mapfre to acquire Safety Insurance in $1.54bn deal, expanding New England reach</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Spanish insurer Mapfre agreed to buy Massachusetts-based Safety Insurance Group in an all-cash $1.54 billion deal at a 44% premium, creating the region's largest homeowners and commercial auto insurer.</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>Insurance Journal</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>https://www.insurancejournal.com/news/east/2026/07/24/878870.htm</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Property &amp; Casualty</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Investments &amp; Funding</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>Zurich secures $1bn reinsurance backstop for its data-center portfolio</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Zurich Insurance entered a new quota-share reinsurance arrangement providing up to $1 billion of capacity to support its fast-growing data-center construction and property book, as AI-driven demand for data-center coverage surges.</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Artemis.bm</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>https://www.artemis.bm/news/zurich-secures-1bn-data-centre-quota-share-breaks-out-us-peak-peril-reinsurance-tower/</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Property &amp; Casualty</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>Market Economics</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>Catastrophe bond issuance smashes records as wildfire-exposed deals surge</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>Cat bond issuance topped $11 billion in the second quarter, the largest quarter on record, with wildfire-exposed issuance for the year climbing past $5 billion as investor appetite for insurance-linked securities keeps growing.</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>Insurance Journal</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>https://www.insurancejournal.com/news/international/2026/08/03/880033.htm</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Brokers &amp; MGA/GA</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Investments &amp; Funding</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>AI-native brokerage platform AGI launches with $70 million to buy up agencies</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>American Growth Insurance launched an AI-enabled brokerage growth platform backed by nearly $70 million in committed equity from Rockbridge Growth Equity and Atomic, and closed its first agency acquisition in Baltimore.</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>Insurance Journal</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>https://www.insurancejournal.com/news/southeast/2026/07/20/878204.htm</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>TPA</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Regulatory &amp; Policy</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>New federal law widens fee-disclosure duties to TPAs and stop-loss insurers</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>The Consolidated Appropriations Act of 2026 expanded compensation-disclosure obligations beyond pharmacy benefit managers to cover third-party administrators, stop-loss insurers and most other group health plan service providers, with penalties up to $10,000 a day for noncompliance.</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>Groom Law Group</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>https://www.groom.com/resources/drug-pricing-and-plan-contracting-practices-under-scrutiny-pbm-and-tpa-reforms-in-the-consolidated-appropriations-act-2026/</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>2026-02-03</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>TPA</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Market Economics</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>Global insurance TPA market keeps expanding as AI-driven claims automation spreads</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>The insurance third-party-administrators market is on track to grow from roughly $372 billion to over $560 billion by 2030, with adoption of AI-driven claims automation and demand for scalable TPA platforms cited as key growth drivers.</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>GlobeNewswire / The Business Research Company</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>https://www.globenewswire.com/news-release/2026/04/27/3281499/28124/en/insurance-third-party-administrators-tpas-global-market-report-2026-yoy-revenue-grew-by-32-billion-ai-driven-claims-automation-to-boost-insurance-tpa-growth-through-2030.html</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>FinTech</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>Investments &amp; Funding</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>Weekly fintech funding cools to $673m across 15 deals</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>Fintech investment pulled back sharply in early August, with $673 million raised across 15 deals, down from more than $2 billion the previous week, though insurance-linked and embedded-finance deals stayed active.</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>FinTech Global</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>https://fintech.global/2026/08/07/a-total-of-673m-was-raised-across-15-fintech-deals-this-week/</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>FinTech</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>Investments &amp; Funding</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>Travel-insurance fintech Faye raises $50m Series C to build an AI travel wallet</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>Faye raised a $50 million Series C led by Madrona at an estimated $500 million valuation, and plans to expand its Faye Wallet product so travelers can manage money and get AI-assisted claims support abroad.</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>FinTech Global</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>https://fintech.global/2026/08/05/faye-raises-50m-to-build-autonomous-travel-care/</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>BrokerTech</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>Technology &amp; AI</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>BrokerTech Ventures sets Chicago convening for late August with growing sponsor lineup</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>BrokerTech Ventures announced BrokerTech Connect: Chicago, running August 31-September 2, bringing together brokers, carriers, investors and insurtech founders for sessions on AI and the next generation of digital-first insurance organizations.</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>PR Newswire</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>https://www.prnewswire.com/news-releases/brokertech-connect-chicago-set-for-august-31september-2-announces-growing-sponsor-lineup-and-industry-programming-302848488.html</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>BrokerTech</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>People &amp; Leadership</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>Jatin Atre named CEO of insurance software provider Insurity</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>Jatin Atre was appointed chief executive officer of Insurity, succeeding Jeff Clarke, after serving as the company's president since the start of 2026.</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>Insurance Business America</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>https://www.insurancebusinessmag.com/us/news/breaking-news/insurance-moves-insurity-crc-benefits-hdi-global-and-epic-580870.aspx</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Insurtech</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>Investments &amp; Funding</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>Global insurtech funding hits $2.44bn in Q2, the strongest quarter since 2022</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>Insurtech funding reached $2.44 billion across 95 deals in the second quarter, the highest quarterly total since 2022, with AI-focused companies capturing nearly all of the available capital, according to Gallagher Re.</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>The Insurer</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>https://www.theinsurer.com/ti/news/insurtech-funding-reaches-244-billion-in-q2-2026-gallagher-re-2026-08-06/</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Insurtech</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Investments &amp; Funding</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>Ahmedabad insurtech InRisk Labs raises $27m Series A</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>InRisk Labs raised $27 million in a Series A round led by Bessemer Venture Partners and Northpoint Capital, after its reinsurance subsidiary EarthRe became the first incorporated reinsurer licensed at GIFT City's International Financial Services Centre.</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>YourStory</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>https://yourstory.com/2026/08/insurtech-startup-inrisk-labs-raises-27-million-in-series-a</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Insurtech</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Technology &amp; AI</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>Insurity and ITS partner to close the insurance industry's technology execution gap</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>Insurity and Insurance Technology Services announced a partnership aimed at reducing delivery risk on insurance technology rollouts, targeting the gap between purchasing new insurance software and actually getting it into production.</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>FinTech Global</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>https://fintech.global/2026/08/12/insurity-and-its-target-the-insurance-industrys-tech-execution-gap/</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Health Insurance / Payer</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>Market Economics</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>Centene swings to $1.1bn Q2 profit, raises 2026 outlook for the second time this year</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>Centene posted $53.6 billion in second-quarter revenue, up 10% year over year, and $1.1 billion in profit, beating expectations as higher premium revenue offset elevated medical costs, prompting another guidance increase.</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>Healthcare Dive</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>https://www.healthcaredive.com/news/centene-cnc-q2-2026-guidance-hike-aca-medicaid/826286/</t>
         </is>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Health Insurance / Payer</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>Technology &amp; AI</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>UnitedHealth's Q2 profit hits $5.4bn as it pours $1.5bn into AI cost controls</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>UnitedHealth Group reported Q2 profit of $5.4 billion and raised its 2026 adjusted EPS guidance, as the insurer works to stabilize margins by shrinking membership, exiting unprofitable contracts and investing $1.5 billion in AI to streamline operations.</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>Forbes</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>https://www.forbes.com/sites/brucejapsen/2026/07/16/unitedhealth-group-profits-hit-54-billion-as-costs-continue-to-ease/</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Healthcare / Provider &amp; Clinical</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>Technology &amp; AI</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>Intermountain Health cuts documentation time 27% with Microsoft's Dragon Copilot</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>Intermountain Health clinicians using Dragon Copilot for 10 or more encounters saw a 27% reduction in time spent on notes per appointment, based on Epic data, as the system scaled the ambient-AI tool across its enterprise.</t>
         </is>
       </c>
-      <c r="G26" s="7" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>Microsoft Customer Stories</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>https://www.microsoft.com/en/customers/story/25891-intermountain-health-microsoft-dragon-copilot</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Healthcare / Provider &amp; Clinical</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>Technology &amp; AI</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>UC Irvine Health warns hospitals often don't know where every AI tool lives in their systems</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>UC Irvine Health's chief medical informatics and AI officer, Dr. Deepti Pandita, said provider organizations may not always know where every AI tool exists in their operations, underscoring the need for system-wide AI awareness and governance.</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>Odgers Berndtson</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>https://www.odgers.com/en-us/insights/ai-operational-governance-an-interview-with-chief-medical-informatics-officer-at-uc-irvine-health-dr-deepti-pandita/</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Healthcare / Provider &amp; Clinical</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>Regulatory &amp; Policy</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>UK/Europe</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>EU opens EUR9m fund for large-scale clinical AI imaging pilots</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>The European Commission's Digital Europe Programme opened a call for proposals worth EUR9 million to fund large-scale pilots of cloud-based AI systems for medical imaging, focused on early detection of cancer and cardiovascular disease in hospitals.</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>European Commission - Digital Strategy</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>https://digital-strategy.ec.europa.eu/en/funding/large-scale-pilots-ai-and-genai-medical-imaging</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Life &amp; Annuities</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>NAIC's life and annuities panel convenes at summer national meeting in Columbus</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>The NAIC Life Insurance and Annuities (A) Committee met August 12 during the 2026 Summer National Meeting in Columbus, Ohio, continuing state regulators' coordination on life and annuity policy priorities.</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>NAIC</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>https://content.naic.org/committees/a/life-insurance-annuities-cmte</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Life &amp; Annuities</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>APAC</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>AIA and Manulife post double-digit new-business growth across Asia</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>AIA's China and Hong Kong operations drove group value of new business up double digits, while Manulife's Asia segment grew core earnings 21% and new business value 13%, both citing strength in Hong Kong, Singapore and mainland China.</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>Insurance Business</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>https://www.insurancebusinessmag.com/asia/news/breaking-news/manulifes-asia-business-grows-core-earnings-21-to-us616-million-in-q2-2026-585128.aspx</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Retirement</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>People &amp; Leadership</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Voya extends 401(k) recordkeeping deal with law firm Baker Botts</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>Voya Financial renewed its role as recordkeeper for international law firm Baker Botts effective August 1, continuing to serve more than 1,800 plan participants and roughly $900 million in retirement assets.</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>PLANADVISER</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>https://www.planadviser.com/advisory-ma-news-8-12-2026/</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Retirement</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>Target-date fund assets climb to $4.8 trillion as collective trusts gain ground</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>Morningstar's latest target-date fund landscape report found TDF assets rose more than 20% year-over-year to $4.8 trillion, with Vanguard holding about 37% of the market as plan sponsors keep shifting toward lower-cost collective investment trusts.</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>Morningstar (via 401(k) Specialist)</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>https://401kspecialistmag.com/4-8-trillion-and-growing-why-traditional-tdfs-are-still-key-to-401k-success/</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Investments &amp; Funding</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Pimco keeps gathering outside assets as parent Allianz deepens its stake</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>Pimco pulled in EUR31.7 billion of third-party net inflows in the second quarter and continued gathering assets into July, Allianz's CFO said, even as the German insurer increases its ownership position in the asset manager.</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>Bloomberg</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/news/articles/2026-08-07/pimco-keeps-pulling-in-money-as-insurer-allianz-boosts-stake</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Artisan Partners reports $183 billion in assets under management</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>Artisan Partners Asset Management disclosed preliminary assets under management of $183.0 billion as of July 31, 2026, giving an early read on mid-year flows for the publicly traded asset manager.</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>SEC filing (Artisan Partners 8-K)</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/0001517302/000151730226000116/apam-20260811.htm</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Wealth Management</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>Wealth Enhancement adds $592 million Illinois RIA Miramar Capital</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>Wealth Enhancement acquired the investment advisory business of Miramar Capital, a Northbrook, Illinois-based independent RIA led by Bob Kalman and Max Wasserman that manages more than $592 million in client assets.</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/wealth-enhancement-announces-acquisition-of-miramar-capital-an-independent-ria-with-over-592-million-in-client-assets-302842284.html</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Wealth Management</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Investments &amp; Funding</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>Carlyle takes minority stake in Prime Capital Financial at $1.8 billion valuation</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>Carlyle's Global Credit platform agreed to roughly a $600 million hybrid capital investment in Prime Capital Financial, valuing the RIA at more than $1.8 billion and letting prior backer Abry Partners exit after three years.</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>InvestmentNews</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>https://www.investmentnews.com/ria-news/carlyle-swoops-in-as-new-prime-capital-backer-valuing-firm-at-18-billion/267735</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Wealth Management</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>People &amp; Leadership</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Family-office wealthtech Asset Vantage names Nicole Eberhardt global CEO</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>Asset Vantage, an AI-led SaaS platform serving more than 400 families across 10 countries, appointed Nicole Eberhardt as global chief executive effective August 1 to lead its next phase of product and international growth.</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>Hubbis</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>https://www.hubbis.com/news/asset-vantage-appoints-nicole-eberhardt-as-global-chief-executive-officer</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>Auto insurance rates resume climbing across more than half of US states</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>After easing in 2025, car insurance premiums are rising again in over half the country, with Connecticut drivers facing the steepest year-over-year increase at 15%, driven by higher repair costs and inflation, per Insurify data.</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>Carrier Management</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>https://www.carriermanagement.com/news/2026/08/13/291037.htm</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>Nevada moves to let home insurers exclude wildfire losses from standard policies</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>Nevada will permit homeowners insurers to carve wildfire coverage out of standard policies starting in 2026, part of a broader wave of state-level moves on wildfire exposure management following record catastrophe losses.</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>AmWINS</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>https://www.amwins.com/resources-and-insights/market-insights/article/state-of-the-market-2026-outlook</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Brokers &amp; MGA/GA</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>UK/Europe</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>Zurich clears final EU antitrust hurdle for GBP8.1 billion Beazley takeover</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>The European Commission approved Zurich Insurance Group's acquisition of Lloyd's insurer Beazley under simplified merger review; the all-cash deal still needs sign-off from UK, Swiss and Lloyd's regulators.</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>Insurance Times</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>https://www.insurancetimes.co.uk/news/european-commission-clears-zurichs-acquisition-of-beazley/1459100.article</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Brokers &amp; MGA/GA</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Investments &amp; Funding</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>Reinsurance sidecars and ILS capital step in as traditional reinsurers pull back from MGAs</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>Broker Gallagher Re says growing use of third-party capital, reinsurance sidecars and insurance-linked-securities investors is helping managing general agents replace underwriting capacity that major reinsurers have scaled back.</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>Artemis</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>https://www.artemis.bm/news/topic/mga/</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>TPA</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>Fiduciary Services Group buys New Jersey retirement-plan TPA RetireWell</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>Fiduciary Services Group, parent of DWC - The 401(k) Experts, acquired Marlton, NJ-based third-party administrator RetireWell Administrators on July 15, its third TPA acquisition of 2026, adding a firm that services more than 425 retirement plans.</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/fiduciary-services-group-acquires-new-jersey-tpa-retirewell-administrators-302826286.html</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>FinTech</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Investments &amp; Funding</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>Fisent Technologies raises $4.3 million to scale AI automation for regulated finance firms</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>Fisent Technologies closed a $4.3 million venture round led by FINTOP, with FINTOP partner John Philpott joining its board, to expand its agentic AI platform for banking, insurance and wealth management workflows.</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>GlobeNewswire</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2026/08/11/3342803/0/en/fisent-technologies-accelerates-growth-with-4-3-million-venture-round-to-expand-adoption-of-applied-genai-process-automation-for-regulated-enterprises.html</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>FinTech</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>UK/Europe</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>Cover Genius buys German insurtech Friendsurance to expand DACH bancassurance push</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>Embedded-protection platform Cover Genius acquired Berlin-based Friendsurance, combining its embedded insurance technology with Friendsurance's digital bancassurance and regulatory expertise across Germany, Austria and Switzerland.</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>FinTech Global</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>https://fintech.global/2026/08/03/cover-genius-acquires-friendsurance-to-expand-dach-banking/</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>FinTech</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>APAC</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>SoftBank's PayPay to acquire 70% of T&amp;D Financial Life in AI-driven insurance push</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>PayPay agreed to acquire a 70.2% stake in T&amp;D Financial Life for about JPY134.3 billion ($838 million) as part of a broader alliance with T&amp;D Holdings to distribute insurance through its super-app and develop AI-powered products for Japan's aging population.</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>Japan Times</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>https://www.japantimes.co.jp/business/2026/06/04/softbank-paypay-td-life-insurer/</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>BrokerTech</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>SUPERAGENT launches 3.0, billed as an AI 'business partner' for insurance agencies</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>SUPERAGENT released version 3.0 on August 11, replacing traditional agency-software navigation with a conversational AI layer that executes calls, campaigns, renewals and training tasks using live agency data.</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>Yahoo Finance / PRWeb</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/technology/ai/articles/superagent-ai-3-0-launches-121700984.html</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Insurtech</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Investments &amp; Funding</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>UK/Europe</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>French digital insurer Alan raises EUR480 million at EUR5.5 billion valuation</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>Alan closed a EUR480 million ($550 million) Series G round led by Prosus, with Ontario Teachers' Pension Plan participating for a third straight round, as the profitable French insurer targets Canada as a growth market.</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>The Next Web</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>https://thenextweb.com/news/alan-480m-prosus-prevention-insurance</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Insurtech</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>AI shifts from insurtech pitch to embedded infrastructure, VCs say</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>Roughly 71% of applicants to the 2026 Global InsurTech Competition referenced AI or automation, but investors say the technology is increasingly treated as infrastructure embedded in underwriting and claims workflows rather than a standalone selling point.</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>InsurTechNY</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>https://www.insurtechny.com/insurtech-trends-2026-ai-insurance-startups/</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Health Insurance / Payer</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>CVS's Caremark settles FTC antitrust case over PBM reimbursement practices</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>CVS Health subsidiaries Caremark Rx and Zinc Health Services agreed to an FTC settlement on July 14 requiring changes to reimbursement practices, making Caremark the second major PBM to resolve enforcement action after Express Scripts settled in February.</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>Federal Trade Commission</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ftc.gov/news-events/news/press-releases/2026/07/ftc-secures-major-settlement-caremark-resolving-antitrust-case-against-second-drug-middleman</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Health Insurance / Payer</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>India weighs national claims exchange and benchmarked treatment rates to curb medical inflation</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>India is considering wide-ranging health insurance reforms, including standardized treatment-rate benchmarks and a nationwide claims exchange, as it seeks to improve transparency amid some of Asia's highest medical inflation.</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>Reuters (via Yahoo News)</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>https://sg.news.yahoo.com/india-plans-insurance-reforms-rein-083021180.html</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>Healthcare / Provider &amp; Clinical</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>Hospital M&amp;A activity rebounds sharply in first half of 2026</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>US hospital and health system mergers rebounded to roughly 40 deals in the first half of 2026, including 18 in the second quarter alone, more than double the same period a year earlier, as systems adjust to new federal and state policy pressures.</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>Chief Healthcare Executive</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>https://www.chiefhealthcareexecutive.com/view/more-hospital-mergers-in-first-half-of-2026-and-momentum-may-continue</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>

--- a/cockpit-data/story-log-last30days.xlsx
+++ b/cockpit-data/story-log-last30days.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Raw Rows (Last 30 Days)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Raw Rows" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,18 +28,25 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="13"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000294D"/>
+        <bgColor rgb="0000294D"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -57,7 +64,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -423,120 +430,230 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Industry Intelligence Cockpit — Last 30 Days Summary</t>
+          <t>Counts by Vertical</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Counts by Lens</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Counts by Week</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Window: 2026-07-31 to 2026-08-29</t>
-        </is>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>lens</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>week</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>16</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Counts by Vertical</t>
-        </is>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Insurtech</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Vertical</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Story Count</t>
-        </is>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Brokers &amp; MGA/GA</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Property &amp; Casualty</t>
+          <t>Health Insurance / Payer</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Investments &amp; Funding</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brokers &amp; MGA/GA</t>
+          <t>Healthcare / Provider &amp; Clinical</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Health Insurance / Payer</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>People &amp; Leadership</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Retirement</t>
+          <t>Wealth Management</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Investments</t>
+          <t>Retirement</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Wealth Management</t>
+          <t>Life &amp; Annuities</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Insurtech</t>
+          <t>Investments</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Healthcare / Provider &amp; Clinical</t>
+          <t>BrokerTech</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -546,149 +663,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Life &amp; Annuities</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>FinTech</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>BrokerTech</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TPA</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Counts by Lens</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Lens</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Story Count</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Market Economics</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>M&amp;A</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Investments &amp; Funding</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Technology &amp; AI</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Regulatory &amp; Policy</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>People &amp; Leadership</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Counts by Week</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>ISO Week</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Story Count</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-W35</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -702,17 +681,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -2408,6 +2387,1181 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Life &amp; Annuities</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Top MYGA fixed annuity rates push above 7% in late August</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>The best available multi-year guaranteed annuity rate reached 7.20% simple interest (6.40% compound) on select terms as of August 27, with every rate change that week moving up rather than down even as the Federal Reserve holds a wait-and-see stance.</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>MyAnnuityStore</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://myannuitystore.com/annuity-rates/fixed-annuity-rates/</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Life &amp; Annuities</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>India advances 100% FDI and policyholder-protection overhaul for insurers</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>IRDAI's 2026 reform package simplifies regulations, strengthens policyholder protection and clears the way for 100% foreign ownership of Indian insurers, with two carriers already raising foreign stakes past the prior 74% cap.</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Vajiram &amp; Ravi</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://vajiramandravi.com/current-affairs/irdai-insurance-sector-reforms-2026/</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Retirement</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Pooled Employer Plan adoption jumps 45% as recordkeepers make PEPs a priority</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>PLANADVISER reports 10,797 employers have now adopted Pooled Employer Plans for 401(k) or 403(b) coverage, up from 7,454 a year earlier, with most recordkeepers now ranking PEPs a major or moderate strategic priority.</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>PLANADVISER</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.planadviser.com/recordkeepers-prioritize-peps-to-spur-growth/</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Retirement</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Neal and Wyden target mega retirement accounts as auto-IRA push continues</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Reps. Richard Neal and Ron Wyden introduced legislation to curb oversized retirement accounts, even as Neal separately continues pushing his long-running Automatic IRA Act to auto-enroll workers without employer plans into IRAs or 401(k)s.</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Congressman Richard Neal (House.gov)</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://neal.house.gov/2026/07/22/neal-wyden-introduce-bill-to-crack-down-on-mega-retirement-accounts/</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>WisdomTree posts sixth straight quarter of record AUM at $162.9 billion</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>WisdomTree's assets under management hit a record $162.9 billion in the second quarter, driven by the Atlantic House acquisition, market appreciation and $3.1 billion of net inflows, marking its sixth consecutive record quarter.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Pulse2.com</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://pulse2.com/wisdomtree-aum-reaches-record-162-9-billion-as-net-inflows-total-3-1-billion/</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Wealth Management</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Apollon and Merit extend RIA buying spree with two more acquisitions</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Apollon Wealth Management added a roughly $650 million RIA while Merit Financial Advisors picked up a $470 million advisory firm, the latest moves in an accelerating wave of RIA consolidation.</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>WealthManagement.com</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://www.wealthmanagement.com/ria-news/deals-moves-apollon-adds-650m-ria-merit-snags-470m-advisory</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Wealth Management</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>MissionSquare pushes beyond retirement plans into personal wealth management</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>MissionSquare, long focused on public-sector retirement plans, launched a personal wealth management business and rebranded its broker-dealer subsidiary as MissionSquare Wealth Management, naming Shannon Hogendorn as president.</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>FinTech Global</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://fintech.global/2026/08/11/missionsquare-expands-into-personal-wealth-management/</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>State Farm raises Illinois home insurance rates 27% on rising claims costs</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>State Farm is raising home insurance rates by an average of 27% for Illinois customers, saying it paid out $1.26 in total costs for every $1 collected in premium in 2024, even as the insurer separately lowers Illinois auto rates.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>CBS News Chicago</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://www.cbsnews.com/chicago/news/state-farm-illinois-home-insurance-rate-hike-august</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Property &amp; Casualty</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>People &amp; Leadership</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>GEICO names Nancy Pierce CEO as insurance leadership shuffle continues</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>GEICO appointed Nancy L. Pierce as chief executive, one of several August leadership changes across the industry that also saw Boston Mutual Life name Grant David Ward CEO and Conduit Holdings name Mark Pickering as incoming CFO.</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Insurance Edge</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://insurance-edge.net/2026/08/24/job-moves-and-senior-appointments-24-08-2026/</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Brokers &amp; MGA/GA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Top five MGA groups now control nearly a fifth of a $17 billion global market</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Brown &amp; Brown, Truist Insurance Holdings, Amwins, Ryan Specialty and Gallagher lead the global MGA, MGU and cover-holder market, which grew roughly 19% to about $17.3 billion in revenue, with Brown &amp; Brown alone topping $1 billion in delegated-underwriting revenue.</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>beinsure.com</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://beinsure.com/top-ranking-mga-worldwide/</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Brokers &amp; MGA/GA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Willis Re agrees to buy BMS Re's US reinsurance division</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Willis Re signed a definitive agreement to acquire the US reinsurance broking and capital-advisory division of BMS Group, calling it a transformational step in accelerating its US expansion.</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Insurance Journal</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://www.insurancejournal.com/news/national/2026/08/19/882135.htm</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>TPA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>TPAs push beyond claims handling into prevention and AI-powered risk management</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Gallagher Bassett argues third-party administrators are shifting from reactive claims processing toward proactive risk prevention, pre-loss consulting and AI-driven claims tools as carriers face rising claim severity and complexity.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Gallagher Bassett</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://insurers.gallagherbassett.com/media/beyond-claims-tpas-push-into-prevention-protection-and-ai-powered-risk-management/</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>FinTech</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>UK/Europe</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Sixfold partners with Sollers Consulting to speed up AI-driven underwriting</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>AI underwriting insurtech Sixfold teamed up with Sollers Consulting to help carriers combine Sixfold's risk-assessment models with Sollers' implementation expertise for faster underwriting transformation.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>FinTech Global</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://fintech.global/2026/08/14/sixfold-and-sollers-team-up-on-ai-underwriting/</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>FinTech</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>UK/Europe</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>EU AI Act's high-risk obligations for insurance underwriting take full effect</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>August 2 marked the date the EU AI Act's high-risk obligations became fully enforceable for uses including credit scoring, insurance underwriting, anti-money-laundering and fraud detection, pushing AI governance to the center of insurers' 2026 strategy.</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>FinTech Global</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://fintech.global/2026/08/04/why-ai-governance-is-shaping-insurances-next-phase/</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>FinTech</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Insurity and ITS team up to close insurers' technology execution gap</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Insurity partnered with ITS to help carriers move past AI experimentation, targeting the persistent gap between insurers' technology ambitions and their ability to actually execute and scale new systems.</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>FinTech Global</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://fintech.global/2026/08/12/insurity-and-its-target-the-insurance-industrys-tech-execution-gap/</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BrokerTech</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Investments &amp; Funding</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>American Growth Insurance launches AI-enabled brokerage growth platform with $70 million backing</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>American Growth Insurance launched an AI-enabled insurance brokerage growth platform with nearly $70 million in committed equity funding from Rockbridge Growth Equity and venture studio Atomic.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/american-growth-insurance-launches-specialty-insurance-brokerage-growth-platform-302827676.html</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Insurtech</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Bolt debuts what it calls the industry's first AI-powered insurance distribution platform</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Bolt launched Connected Distribution, an AI-driven operating model meant to unify customer data, workflows and market access across all lines of business for its distribution partners.</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>FinTech Global</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://fintech.global/2026/08/19/bolt-debuts-industry-first-ai-insurance-platform/</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Insurtech</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Carpe launches Minerva Reasoning Engine to help small commercial insurers underwrite profitably</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>AI-native data specialist Carpe introduced its Minerva Reasoning Engine, an underwriting tool aimed specifically at helping small commercial insurers price risk more profitably.</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>FinTech Global</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://fintech.global/2026/08/24/carpe-launches-ai-underwriting-tool-for-insurers/</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Insurtech</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AI adoption and global shocks combine to push insurance pricing higher</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Insurers are citing both the rising cost of AI adoption and a run of global economic and geopolitical shocks as combined pressures pushing premium pricing upward across several lines.</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>FinTech Global</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://fintech.global/2026/08/18/ai-and-global-shocks-put-pressure-on-insurance-pricing/</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Insurtech</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Investments &amp; Funding</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>APAC</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Tokio Marine takes minority stake in Singapore insurtech Igloo</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tokio Marine invested about $5 million for a 1.65% equity stake in Igloo, a full-stack insurtech operating across eight Southeast Asian markets, extending the Japanese carrier's push deeper into the region's digital insurance space.</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Insurance Business Asia</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://www.insurancebusinessmag.com/asia/news/technology/tokio-marine-buys-minority-stake-in-singapore-insurtech-igloo-563467.aspx</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Health Insurance / Payer</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Regulatory &amp; Policy</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>CMS backs off proposed Medicare Advantage payment cut, raising 2027 rates nearly 5%</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>CMS finalized Medicare Advantage payment rates for 2027 well above its initial proposal, delivering private insurers close to a 5% average per-enrollee increase after industry pushback on planned cuts.</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>KFF</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://www.kff.org/quick-take/medicare-advantage-insurers-will-see-higher-payments-as-cms-backs-off-a-key-payment-update/</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Health Insurance / Payer</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Market Economics</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Insurer exits keep thinning Medicare Advantage options for enrollees</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Becker's Payer Issues tracks a continuing pattern of Medicare Advantage insurer exits and pullbacks in 2026, with a JAMA study finding roughly 10% of MA enrollees had to disenroll and find new coverage after their plans left the market.</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Becker's Payer Issues</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://www.beckerspayer.com/payer/medicare-advantage/5-insurers-stepping-back-from-medicare-advantage/</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Healthcare / Provider &amp; Clinical</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Innovaccer and AWS strike multi-year deal to scale agentic AI across health systems</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Innovaccer and Amazon Web Services signed a multi-year strategic collaboration aimed at helping health systems and payers move agentic AI from pilot projects into deployments that meet security, compliance and scale requirements.</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Fierce Healthcare</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://www.fiercehealthcare.com/health-tech/weekly-rundown-innovaccer-aws-ink-strategic-collab-invoca-launches-patient-engagement</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Healthcare / Provider &amp; Clinical</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Technology &amp; AI</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Exer AI expands Mayo Clinic partnership to widen clinical AI tool deployment</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Exer AI broadened its partnership with Mayo Clinic to further integrate its AI-powered movement-assessment technology into orthopaedic clinical workflows.</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Digital Health News</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://www.digitalhealthnews.com/exer-ai-expands-mayo-clinic-partnership-to-advance-clinical-ai-tool-deployment</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Healthcare / Provider &amp; Clinical</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Atrium Health and WakeMed plan combination with $2 billion investment pledge</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Atrium Health, part of Advocate Health, is planning to join forces with WakeMed, pledging $2 billion in investments across Wake County and vowing to create more than 3,000 jobs as large health-system tie-ups continue in 2026.</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Becker's Hospital Review</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.beckershospitalreview.com/rural-health/growth-merger/11-large-health-systems-growing-bigger/</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
